--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -749,6 +749,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -758,7 +761,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -919,6 +922,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -962,7 +968,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1124,6 +1130,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1133,7 +1142,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1295,6 +1304,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1681068.5808443392</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1717781.1968650564</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1337,7 +1349,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1499,6 +1511,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1508,7 +1523,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1670,6 +1685,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>522575.55136211542</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>559288.16738283262</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1691,11 +1709,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="476349952"/>
-        <c:axId val="476351488"/>
+        <c:axId val="590738560"/>
+        <c:axId val="590740096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="476349952"/>
+        <c:axId val="590738560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1738,14 +1756,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="476351488"/>
+        <c:crossAx val="590740096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="476351488"/>
+        <c:axId val="590740096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1796,7 +1814,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="476349952"/>
+        <c:crossAx val="590738560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1957,7 +1975,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2119,6 +2137,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-20790.629041221724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2138,8 +2159,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="472072960"/>
-        <c:axId val="472062976"/>
+        <c:axId val="522601984"/>
+        <c:axId val="522600448"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2164,7 +2185,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2326,6 +2347,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2335,7 +2359,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2497,6 +2521,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2518,11 +2545,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472059904"/>
-        <c:axId val="472061440"/>
+        <c:axId val="522584832"/>
+        <c:axId val="522586368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472059904"/>
+        <c:axId val="522584832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2565,14 +2592,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472061440"/>
+        <c:crossAx val="522586368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472061440"/>
+        <c:axId val="522586368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2623,12 +2650,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472059904"/>
+        <c:crossAx val="522584832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="472062976"/>
+        <c:axId val="522600448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2665,12 +2692,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472072960"/>
+        <c:crossAx val="522601984"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="472072960"/>
+        <c:axId val="522601984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2679,7 +2706,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="472062976"/>
+        <c:crossAx val="522600448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2829,7 +2856,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2991,6 +3018,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3000,7 +3030,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3161,6 +3191,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3204,7 +3237,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3366,6 +3399,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3375,7 +3411,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3537,6 +3573,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13294599.184037466</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>13593904.720455116</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3579,7 +3618,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3741,6 +3780,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3750,7 +3792,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3912,6 +3954,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5018959.1907411907</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5318264.7271588407</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3933,11 +3978,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472100864"/>
-        <c:axId val="472102400"/>
+        <c:axId val="522846976"/>
+        <c:axId val="522848512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472100864"/>
+        <c:axId val="522846976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3980,14 +4025,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472102400"/>
+        <c:crossAx val="522848512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472102400"/>
+        <c:axId val="522848512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4038,7 +4083,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472100864"/>
+        <c:crossAx val="522846976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4199,7 +4244,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4361,6 +4406,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-18333.497294467583</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-46393.241034391052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4380,8 +4428,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="473121920"/>
-        <c:axId val="473107840"/>
+        <c:axId val="522897280"/>
+        <c:axId val="522895744"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4406,7 +4454,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4568,6 +4616,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4577,7 +4628,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4739,6 +4790,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4760,11 +4814,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="473104768"/>
-        <c:axId val="473106304"/>
+        <c:axId val="522884224"/>
+        <c:axId val="522885760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="473104768"/>
+        <c:axId val="522884224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4807,14 +4861,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473106304"/>
+        <c:crossAx val="522885760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="473106304"/>
+        <c:axId val="522885760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4865,12 +4919,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473104768"/>
+        <c:crossAx val="522884224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="473107840"/>
+        <c:axId val="522895744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4907,12 +4961,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473121920"/>
+        <c:crossAx val="522897280"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="473121920"/>
+        <c:axId val="522897280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4921,7 +4975,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="473107840"/>
+        <c:crossAx val="522895744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5071,7 +5125,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5233,6 +5287,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5242,7 +5299,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5403,6 +5460,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5446,7 +5506,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5608,6 +5668,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5617,7 +5680,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5779,6 +5842,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13918241.906652076</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14227459.764016345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5821,7 +5887,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5983,6 +6049,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5992,7 +6061,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6154,6 +6223,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4556907.088924652</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4866124.9462889209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6175,11 +6247,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475169152"/>
-        <c:axId val="475170688"/>
+        <c:axId val="528270848"/>
+        <c:axId val="528272384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475169152"/>
+        <c:axId val="528270848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6222,14 +6294,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475170688"/>
+        <c:crossAx val="528272384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475170688"/>
+        <c:axId val="528272384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6280,7 +6352,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475169152"/>
+        <c:crossAx val="528270848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6441,7 +6513,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6603,6 +6675,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6622,8 +6697,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="476333568"/>
-        <c:axId val="476332032"/>
+        <c:axId val="528370304"/>
+        <c:axId val="528368768"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6648,7 +6723,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6810,6 +6885,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6819,7 +6897,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -6981,6 +7059,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7002,11 +7083,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475198208"/>
-        <c:axId val="475199744"/>
+        <c:axId val="528365440"/>
+        <c:axId val="528366976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475198208"/>
+        <c:axId val="528365440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7049,14 +7130,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475199744"/>
+        <c:crossAx val="528366976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475199744"/>
+        <c:axId val="528366976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7107,12 +7188,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475198208"/>
+        <c:crossAx val="528365440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="476332032"/>
+        <c:axId val="528368768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7149,12 +7230,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="476333568"/>
+        <c:crossAx val="528370304"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="476333568"/>
+        <c:axId val="528370304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7163,7 +7244,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="476332032"/>
+        <c:crossAx val="528368768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7295,7 +7376,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7457,6 +7538,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-20790.629041221724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7476,8 +7560,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="535829504"/>
-        <c:axId val="535827968"/>
+        <c:axId val="669702784"/>
+        <c:axId val="669701248"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7502,7 +7586,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7664,6 +7748,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7673,7 +7760,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7835,6 +7922,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7856,11 +7946,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="533718912"/>
-        <c:axId val="533720448"/>
+        <c:axId val="669517312"/>
+        <c:axId val="669518848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="533718912"/>
+        <c:axId val="669517312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7903,14 +7993,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533720448"/>
+        <c:crossAx val="669518848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533720448"/>
+        <c:axId val="669518848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7961,12 +8051,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533718912"/>
+        <c:crossAx val="669517312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="535827968"/>
+        <c:axId val="669701248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8003,12 +8093,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535829504"/>
+        <c:crossAx val="669702784"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="535829504"/>
+        <c:axId val="669702784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8017,7 +8107,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="535827968"/>
+        <c:crossAx val="669701248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8167,7 +8257,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8329,6 +8419,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8338,7 +8431,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8499,6 +8592,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -8542,7 +8638,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8704,6 +8800,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8713,7 +8812,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8875,6 +8974,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1892332.1802078688</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1934291.8223967806</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8917,7 +9019,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9079,6 +9181,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9088,7 +9193,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9250,6 +9355,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>572440.58810827555</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>614400.23029718734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9271,11 +9379,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="540418048"/>
-        <c:axId val="540419584"/>
+        <c:axId val="433236224"/>
+        <c:axId val="433459200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="540418048"/>
+        <c:axId val="433236224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9318,14 +9426,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="540419584"/>
+        <c:crossAx val="433459200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="540419584"/>
+        <c:axId val="433459200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9376,7 +9484,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="540418048"/>
+        <c:crossAx val="433236224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9558,7 +9666,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9720,6 +9828,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-4158.1258082443446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9739,8 +9850,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="99507200"/>
-        <c:axId val="99505664"/>
+        <c:axId val="433496064"/>
+        <c:axId val="433494272"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9765,7 +9876,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9927,6 +10038,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9936,7 +10050,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10098,6 +10212,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10119,11 +10236,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99502336"/>
-        <c:axId val="99504128"/>
+        <c:axId val="433490944"/>
+        <c:axId val="433492736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99502336"/>
+        <c:axId val="433490944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10166,14 +10283,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99504128"/>
+        <c:crossAx val="433492736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="99504128"/>
+        <c:axId val="433492736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10224,12 +10341,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99502336"/>
+        <c:crossAx val="433490944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="99505664"/>
+        <c:axId val="433494272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10266,12 +10383,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99507200"/>
+        <c:crossAx val="433496064"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="99507200"/>
+        <c:axId val="433496064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10280,7 +10397,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="99505664"/>
+        <c:crossAx val="433494272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10430,7 +10547,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10592,6 +10709,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10601,7 +10721,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10762,6 +10882,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -10805,7 +10928,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10967,6 +11090,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10976,7 +11102,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11138,6 +11264,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>16004082.547668742</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16362949.816239173</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11180,7 +11309,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11342,6 +11471,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11351,7 +11483,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11513,6 +11645,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5116246.7741877642</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5475114.0427581947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11534,11 +11669,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="312883456"/>
-        <c:axId val="312901632"/>
+        <c:axId val="447781888"/>
+        <c:axId val="447783680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="312883456"/>
+        <c:axId val="447781888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11581,14 +11716,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="312901632"/>
+        <c:crossAx val="447783680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="312901632"/>
+        <c:axId val="447783680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11639,7 +11774,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="312883456"/>
+        <c:crossAx val="447781888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11821,7 +11956,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11983,6 +12118,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-21886.088907832516</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12002,8 +12140,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="469406080"/>
-        <c:axId val="312928896"/>
+        <c:axId val="452592384"/>
+        <c:axId val="447806464"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12028,7 +12166,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12190,6 +12328,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12199,7 +12340,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12361,6 +12502,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12382,11 +12526,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="312921472"/>
-        <c:axId val="312927360"/>
+        <c:axId val="447803392"/>
+        <c:axId val="447804928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="312921472"/>
+        <c:axId val="447803392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12429,14 +12573,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="312927360"/>
+        <c:crossAx val="447804928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="312927360"/>
+        <c:axId val="447804928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12487,12 +12631,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="312921472"/>
+        <c:crossAx val="447803392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="312928896"/>
+        <c:axId val="447806464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12529,12 +12673,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469406080"/>
+        <c:crossAx val="452592384"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="469406080"/>
+        <c:axId val="452592384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12543,7 +12687,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="312928896"/>
+        <c:crossAx val="447806464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12693,7 +12837,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12855,6 +12999,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12864,7 +13011,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13025,6 +13172,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13068,7 +13218,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13230,6 +13380,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13239,7 +13392,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13401,6 +13554,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>2111236.7158821402</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2159110.7382003833</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13443,7 +13599,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13605,6 +13761,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13614,7 +13773,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13776,6 +13935,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>792141.12421423499</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>840015.14653247804</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13797,11 +13959,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="469450112"/>
-        <c:axId val="469456000"/>
+        <c:axId val="452640768"/>
+        <c:axId val="452642304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="469450112"/>
+        <c:axId val="452640768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13844,14 +14006,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469456000"/>
+        <c:crossAx val="452642304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="469456000"/>
+        <c:axId val="452642304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13902,7 +14064,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469450112"/>
+        <c:crossAx val="452640768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14063,7 +14225,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14225,6 +14387,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-2552.7654460651065</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-1291.963674375447</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14244,8 +14409,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="469488384"/>
-        <c:axId val="469478400"/>
+        <c:axId val="521692288"/>
+        <c:axId val="521686400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14270,7 +14435,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14432,6 +14597,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14441,7 +14609,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -14603,6 +14771,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14624,11 +14795,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="469475328"/>
-        <c:axId val="469476864"/>
+        <c:axId val="521683328"/>
+        <c:axId val="521684864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="469475328"/>
+        <c:axId val="521683328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14671,14 +14842,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469476864"/>
+        <c:crossAx val="521684864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="469476864"/>
+        <c:axId val="521684864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14729,12 +14900,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469475328"/>
+        <c:crossAx val="521683328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="469478400"/>
+        <c:axId val="521686400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14771,12 +14942,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="469488384"/>
+        <c:crossAx val="521692288"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="469488384"/>
+        <c:axId val="521692288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14785,7 +14956,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="469478400"/>
+        <c:crossAx val="521686400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14935,7 +15106,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15097,6 +15268,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15106,7 +15280,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15267,6 +15441,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -15310,7 +15487,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15472,6 +15649,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15481,7 +15661,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15643,6 +15823,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1707604.5820033031</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1744929.5685449983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15685,7 +15868,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15847,6 +16030,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15856,7 +16042,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16018,6 +16204,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>532792.78610775061</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>570117.7726494458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16039,11 +16228,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="471965056"/>
-        <c:axId val="471966848"/>
+        <c:axId val="522559872"/>
+        <c:axId val="522561408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="471965056"/>
+        <c:axId val="522559872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16086,14 +16275,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="471966848"/>
+        <c:crossAx val="522561408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="471966848"/>
+        <c:axId val="522561408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16144,7 +16333,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="471965056"/>
+        <c:crossAx val="522559872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17080,7 +17269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -19495,6 +19684,44 @@
         <v>90191.835636928721</v>
       </c>
     </row>
+    <row r="57" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="32">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="31">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="29">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="29">
+        <v>-20790.629041221724</v>
+      </c>
+      <c r="F57" s="30">
+        <v>-19540.064695712677</v>
+      </c>
+      <c r="G57" s="30">
+        <v>1510149.1694970026</v>
+      </c>
+      <c r="H57" s="30">
+        <v>1606798.732186906</v>
+      </c>
+      <c r="I57" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J57" s="30">
+        <v>1717781.1968650564</v>
+      </c>
+      <c r="K57" s="30">
+        <v>559288.16738283262</v>
+      </c>
+      <c r="L57" s="29">
+        <v>110982.46467815044</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19511,7 +19738,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -22555,6 +22782,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-4158.1258082443446</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-3908.0129391425353</v>
+      </c>
+      <c r="G57" s="18">
+        <v>1744406.8685374688</v>
+      </c>
+      <c r="H57" s="18">
+        <v>1856048.9264234232</v>
+      </c>
+      <c r="I57" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J57" s="18">
+        <v>1934291.8223967806</v>
+      </c>
+      <c r="K57" s="18">
+        <v>614400.23029718734</v>
+      </c>
+      <c r="L57" s="17">
+        <v>78242.895973357343</v>
+      </c>
+      <c r="M57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="N57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="O57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -22571,7 +22848,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25615,6 +25892,56 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-21886.088907832516</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-20569.632229368879</v>
+      </c>
+      <c r="G57" s="18">
+        <v>14932202.922212096</v>
+      </c>
+      <c r="H57" s="18">
+        <v>15887864.065878714</v>
+      </c>
+      <c r="I57" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J57" s="18">
+        <v>16362949.816239173</v>
+      </c>
+      <c r="K57" s="18">
+        <v>5475114.0427581947</v>
+      </c>
+      <c r="L57" s="17">
+        <v>475085.75036045833</v>
+      </c>
+      <c r="M57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="N57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="O57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -25631,7 +25958,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29011,6 +29338,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="17">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="17">
+        <v>-1291.963674375447</v>
+      </c>
+      <c r="H57" s="18">
+        <v>-1214.2515616893245</v>
+      </c>
+      <c r="I57" s="18">
+        <v>1993532.6358949887</v>
+      </c>
+      <c r="J57" s="18">
+        <v>2121118.7455052575</v>
+      </c>
+      <c r="K57" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L57" s="18">
+        <v>2159110.7382003833</v>
+      </c>
+      <c r="M57" s="18">
+        <v>840015.14653247804</v>
+      </c>
+      <c r="N57" s="17">
+        <v>37991.992695125584</v>
+      </c>
+      <c r="O57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="P57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="Q57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -29027,7 +29410,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -32252,6 +32635,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="57" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-20790.629041221724</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-19540.064695712677</v>
+      </c>
+      <c r="G57" s="18">
+        <v>1535664.5561626744</v>
+      </c>
+      <c r="H57" s="18">
+        <v>1633947.1038668479</v>
+      </c>
+      <c r="I57" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J57" s="18">
+        <v>1744929.5685449983</v>
+      </c>
+      <c r="K57" s="18">
+        <v>570117.7726494458</v>
+      </c>
+      <c r="L57" s="17">
+        <v>110982.46467815044</v>
+      </c>
+      <c r="M57" s="21">
+        <v>82.317072210415034</v>
+      </c>
+      <c r="N57" s="21">
+        <v>82.130142596708495</v>
+      </c>
+      <c r="O57" s="21">
+        <v>81.483167688714857</v>
+      </c>
+      <c r="P57" s="21">
+        <v>83.424092412695785</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -32268,7 +32704,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35016,6 +35452,50 @@
         <v>324719.36588530202</v>
       </c>
     </row>
+    <row r="57" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="17">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="17">
+        <v>-46393.241034391052</v>
+      </c>
+      <c r="H57" s="18">
+        <v>-43602.669715207558</v>
+      </c>
+      <c r="I57" s="18">
+        <v>12427436.07440454</v>
+      </c>
+      <c r="J57" s="18">
+        <v>13222792.113535423</v>
+      </c>
+      <c r="K57" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L57" s="18">
+        <v>13593904.720455116</v>
+      </c>
+      <c r="M57" s="18">
+        <v>5318264.7271588407</v>
+      </c>
+      <c r="N57" s="17">
+        <v>371112.60691969306</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -35032,7 +35512,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37447,6 +37927,44 @@
         <v>518829.06704185653</v>
       </c>
     </row>
+    <row r="57" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="18">
+        <v>12781203.118754858</v>
+      </c>
+      <c r="H57" s="18">
+        <v>13599200.252435327</v>
+      </c>
+      <c r="I57" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J57" s="18">
+        <v>14227459.764016345</v>
+      </c>
+      <c r="K57" s="18">
+        <v>4866124.9462889209</v>
+      </c>
+      <c r="L57" s="17">
+        <v>628259.51158101915</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -752,6 +752,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -761,7 +764,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -925,6 +928,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -968,7 +974,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1133,6 +1139,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1142,7 +1151,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1307,6 +1316,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1717781.1968650564</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1729862.4147042707</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1349,7 +1361,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1514,6 +1526,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1523,7 +1538,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1688,6 +1703,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>559288.16738283262</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>571369.38522204687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1709,11 +1727,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="590738560"/>
-        <c:axId val="590740096"/>
+        <c:axId val="564126848"/>
+        <c:axId val="564128384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="590738560"/>
+        <c:axId val="564126848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1756,14 +1774,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590740096"/>
+        <c:crossAx val="564128384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="590740096"/>
+        <c:axId val="564128384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1814,7 +1832,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="590738560"/>
+        <c:crossAx val="564126848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1975,7 +1993,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2140,6 +2158,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-20790.629041221724</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2159,8 +2180,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522601984"/>
-        <c:axId val="522600448"/>
+        <c:axId val="530166912"/>
+        <c:axId val="530152832"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2185,7 +2206,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2350,6 +2371,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2359,7 +2383,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2524,6 +2548,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2545,11 +2572,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522584832"/>
-        <c:axId val="522586368"/>
+        <c:axId val="530149760"/>
+        <c:axId val="530151296"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522584832"/>
+        <c:axId val="530149760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2592,14 +2619,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522586368"/>
+        <c:crossAx val="530151296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522586368"/>
+        <c:axId val="530151296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2650,12 +2677,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522584832"/>
+        <c:crossAx val="530149760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522600448"/>
+        <c:axId val="530152832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2692,12 +2719,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522601984"/>
+        <c:crossAx val="530166912"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522601984"/>
+        <c:axId val="530166912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2706,7 +2733,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522600448"/>
+        <c:crossAx val="530152832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2856,7 +2883,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3021,6 +3048,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3030,7 +3060,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3194,6 +3224,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3237,7 +3270,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3402,6 +3435,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3411,7 +3447,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3576,6 +3612,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>13593904.720455116</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>13693324.410529703</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3618,7 +3657,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3783,6 +3822,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3792,7 +3834,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3957,6 +3999,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5318264.7271588407</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5417684.417233428</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3978,11 +4023,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522846976"/>
-        <c:axId val="522848512"/>
+        <c:axId val="543072640"/>
+        <c:axId val="543074176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522846976"/>
+        <c:axId val="543072640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4025,14 +4070,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522848512"/>
+        <c:crossAx val="543074176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522848512"/>
+        <c:axId val="543074176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4083,7 +4128,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522846976"/>
+        <c:crossAx val="543072640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4244,7 +4289,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4409,6 +4454,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-46393.241034391052</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-111127.31971233143</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4428,8 +4476,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522897280"/>
-        <c:axId val="522895744"/>
+        <c:axId val="543774208"/>
+        <c:axId val="543772672"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4454,7 +4502,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4619,6 +4667,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4628,7 +4679,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4793,6 +4844,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4814,11 +4868,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522884224"/>
-        <c:axId val="522885760"/>
+        <c:axId val="543765248"/>
+        <c:axId val="543766784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522884224"/>
+        <c:axId val="543765248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4861,14 +4915,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522885760"/>
+        <c:crossAx val="543766784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522885760"/>
+        <c:axId val="543766784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4919,12 +4973,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522884224"/>
+        <c:crossAx val="543765248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522895744"/>
+        <c:axId val="543772672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4961,12 +5015,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522897280"/>
+        <c:crossAx val="543774208"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522897280"/>
+        <c:axId val="543774208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4975,7 +5029,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522895744"/>
+        <c:crossAx val="543772672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5125,7 +5179,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5290,6 +5344,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5299,7 +5356,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5463,6 +5520,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5506,7 +5566,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5671,6 +5731,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5680,7 +5743,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5845,6 +5908,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>14227459.764016345</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14329709.596181171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5887,7 +5953,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6052,6 +6118,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6061,7 +6130,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6226,6 +6295,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>4866124.9462889209</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4968374.7784537468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6247,11 +6319,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528270848"/>
-        <c:axId val="528272384"/>
+        <c:axId val="556012288"/>
+        <c:axId val="556013824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528270848"/>
+        <c:axId val="556012288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6294,14 +6366,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528272384"/>
+        <c:crossAx val="556013824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528272384"/>
+        <c:axId val="556013824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6352,7 +6424,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528270848"/>
+        <c:crossAx val="556012288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6513,7 +6585,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6678,6 +6750,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6697,8 +6772,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="528370304"/>
-        <c:axId val="528368768"/>
+        <c:axId val="556058496"/>
+        <c:axId val="556056960"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6723,7 +6798,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6888,6 +6963,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6897,7 +6975,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7062,6 +7140,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7083,11 +7164,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528365440"/>
-        <c:axId val="528366976"/>
+        <c:axId val="556049536"/>
+        <c:axId val="556051072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528365440"/>
+        <c:axId val="556049536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7130,14 +7211,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528366976"/>
+        <c:crossAx val="556051072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528366976"/>
+        <c:axId val="556051072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7188,12 +7269,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528365440"/>
+        <c:crossAx val="556049536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="528368768"/>
+        <c:axId val="556056960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7230,12 +7311,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528370304"/>
+        <c:crossAx val="556058496"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="528370304"/>
+        <c:axId val="556058496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7244,7 +7325,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="528368768"/>
+        <c:crossAx val="556056960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7376,7 +7457,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7541,6 +7622,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-20790.629041221724</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7560,8 +7644,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="669702784"/>
-        <c:axId val="669701248"/>
+        <c:axId val="609222656"/>
+        <c:axId val="609200000"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7586,7 +7670,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7751,6 +7835,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7760,7 +7847,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7925,6 +8012,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7946,11 +8036,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="669517312"/>
-        <c:axId val="669518848"/>
+        <c:axId val="609114752"/>
+        <c:axId val="609198464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="669517312"/>
+        <c:axId val="609114752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7993,14 +8083,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669518848"/>
+        <c:crossAx val="609198464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="669518848"/>
+        <c:axId val="609198464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8051,12 +8141,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669517312"/>
+        <c:crossAx val="609114752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="669701248"/>
+        <c:axId val="609200000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8093,12 +8183,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669702784"/>
+        <c:crossAx val="609222656"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="669702784"/>
+        <c:axId val="609222656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8107,7 +8197,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="669701248"/>
+        <c:crossAx val="609200000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8257,7 +8347,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8422,6 +8512,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8431,7 +8524,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8595,6 +8688,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -8638,7 +8734,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8803,6 +8899,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8812,7 +8911,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8977,6 +9076,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1934291.8223967806</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1948247.1056262129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9019,7 +9121,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9184,6 +9286,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9193,7 +9298,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9358,6 +9463,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>614400.23029718734</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>628355.51352661964</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9379,11 +9487,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433236224"/>
-        <c:axId val="433459200"/>
+        <c:axId val="662115840"/>
+        <c:axId val="662117376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433236224"/>
+        <c:axId val="662115840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9426,14 +9534,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433459200"/>
+        <c:crossAx val="662117376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433459200"/>
+        <c:axId val="662117376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9484,7 +9592,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433236224"/>
+        <c:crossAx val="662115840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9666,7 +9774,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9831,6 +9939,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-4158.1258082443446</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-4531.947395988238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9850,8 +9961,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="433496064"/>
-        <c:axId val="433494272"/>
+        <c:axId val="529649024"/>
+        <c:axId val="529647488"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9876,7 +9987,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10041,6 +10152,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10050,7 +10164,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10215,6 +10329,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10236,11 +10353,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433490944"/>
-        <c:axId val="433492736"/>
+        <c:axId val="529640064"/>
+        <c:axId val="529645952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433490944"/>
+        <c:axId val="529640064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10283,14 +10400,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433492736"/>
+        <c:crossAx val="529645952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433492736"/>
+        <c:axId val="529645952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10341,12 +10458,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433490944"/>
+        <c:crossAx val="529640064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="433494272"/>
+        <c:axId val="529647488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10383,12 +10500,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433496064"/>
+        <c:crossAx val="529649024"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="433496064"/>
+        <c:axId val="529649024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10397,7 +10514,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="433494272"/>
+        <c:crossAx val="529647488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10547,7 +10664,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10712,6 +10829,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10721,7 +10841,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10885,6 +11005,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -10928,7 +11051,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11093,6 +11216,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11102,7 +11228,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11267,6 +11393,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>16362949.816239173</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16482407.681704661</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11309,7 +11438,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11474,6 +11603,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11483,7 +11615,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11648,6 +11780,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5475114.0427581947</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5594571.908223683</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11669,11 +11804,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="447781888"/>
-        <c:axId val="447783680"/>
+        <c:axId val="529668736"/>
+        <c:axId val="529674624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="447781888"/>
+        <c:axId val="529668736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11716,14 +11851,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447783680"/>
+        <c:crossAx val="529674624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="447783680"/>
+        <c:axId val="529674624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11774,7 +11909,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447781888"/>
+        <c:crossAx val="529668736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11956,7 +12091,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12121,6 +12256,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-21886.088907832516</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-25998.161012664015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12140,8 +12278,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="452592384"/>
-        <c:axId val="447806464"/>
+        <c:axId val="529699584"/>
+        <c:axId val="529697792"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12166,7 +12304,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12331,6 +12469,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12340,7 +12481,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12505,6 +12646,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12526,11 +12670,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="447803392"/>
-        <c:axId val="447804928"/>
+        <c:axId val="529694720"/>
+        <c:axId val="529696256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="447803392"/>
+        <c:axId val="529694720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12573,14 +12717,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447804928"/>
+        <c:crossAx val="529696256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="447804928"/>
+        <c:axId val="529696256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12631,12 +12775,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="447803392"/>
+        <c:crossAx val="529694720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="447806464"/>
+        <c:axId val="529697792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12673,12 +12817,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452592384"/>
+        <c:crossAx val="529699584"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="452592384"/>
+        <c:axId val="529699584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12687,7 +12831,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="447806464"/>
+        <c:crossAx val="529697792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12837,7 +12981,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13002,6 +13146,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13011,7 +13158,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13175,6 +13322,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13218,7 +13368,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13383,6 +13533,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13392,7 +13545,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13557,6 +13710,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>2159110.7382003833</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2175059.0316076181</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13599,7 +13755,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13764,6 +13920,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13773,7 +13932,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13938,6 +14097,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>840015.14653247804</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>855963.43993971287</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13959,11 +14121,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="452640768"/>
-        <c:axId val="452642304"/>
+        <c:axId val="530042880"/>
+        <c:axId val="530044416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="452640768"/>
+        <c:axId val="530042880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14006,14 +14168,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452642304"/>
+        <c:crossAx val="530044416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="452642304"/>
+        <c:axId val="530044416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14064,7 +14226,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="452640768"/>
+        <c:crossAx val="530042880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14225,7 +14387,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14390,6 +14552,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-1291.963674375447</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-3094.6848527484703</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14409,8 +14574,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="521692288"/>
-        <c:axId val="521686400"/>
+        <c:axId val="530109568"/>
+        <c:axId val="530107776"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14435,7 +14600,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14600,6 +14765,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14609,7 +14777,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -14774,6 +14942,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14795,11 +14966,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521683328"/>
-        <c:axId val="521684864"/>
+        <c:axId val="530104704"/>
+        <c:axId val="530106240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521683328"/>
+        <c:axId val="530104704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14842,14 +15013,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521684864"/>
+        <c:crossAx val="530106240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521684864"/>
+        <c:axId val="530106240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14900,12 +15071,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521683328"/>
+        <c:crossAx val="530104704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="521686400"/>
+        <c:axId val="530107776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14942,12 +15113,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521692288"/>
+        <c:crossAx val="530109568"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="521692288"/>
+        <c:axId val="530109568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14956,7 +15127,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="521686400"/>
+        <c:crossAx val="530107776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15106,7 +15277,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15271,6 +15442,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15280,7 +15454,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15444,6 +15618,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -15487,7 +15664,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15652,6 +15829,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15661,7 +15841,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15826,6 +16006,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1744929.5685449983</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1757214.9098912054</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15868,7 +16051,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16033,6 +16216,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16042,7 +16228,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16207,6 +16393,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>570117.7726494458</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>582403.11399565288</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16228,11 +16417,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522559872"/>
-        <c:axId val="522561408"/>
+        <c:axId val="530137088"/>
+        <c:axId val="530138624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522559872"/>
+        <c:axId val="530137088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16275,14 +16464,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522561408"/>
+        <c:crossAx val="530138624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522561408"/>
+        <c:axId val="530138624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16333,7 +16522,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522559872"/>
+        <c:crossAx val="530137088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16434,7 +16623,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16472,7 +16661,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16515,7 +16704,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16553,7 +16742,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16596,7 +16785,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16634,7 +16823,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16677,7 +16866,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16715,7 +16904,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16758,7 +16947,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16796,7 +16985,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16839,7 +17028,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16877,7 +17066,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16920,7 +17109,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16958,7 +17147,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17269,7 +17458,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -19722,6 +19911,44 @@
         <v>110982.46467815044</v>
       </c>
     </row>
+    <row r="58" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="32">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="31">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="29">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="29">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F58" s="30">
+        <v>-21137.813820429725</v>
+      </c>
+      <c r="G58" s="30">
+        <v>1489011.355676573</v>
+      </c>
+      <c r="H58" s="30">
+        <v>1596220.2130461792</v>
+      </c>
+      <c r="I58" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J58" s="30">
+        <v>1729862.4147042707</v>
+      </c>
+      <c r="K58" s="30">
+        <v>571369.38522204687</v>
+      </c>
+      <c r="L58" s="29">
+        <v>133642.20165809162</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19738,7 +19965,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -22832,6 +23059,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="58" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-4531.947395988238</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-4227.5627640859448</v>
+      </c>
+      <c r="G58" s="18">
+        <v>1740179.305773383</v>
+      </c>
+      <c r="H58" s="18">
+        <v>1865472.2622568673</v>
+      </c>
+      <c r="I58" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J58" s="18">
+        <v>1948247.1056262129</v>
+      </c>
+      <c r="K58" s="18">
+        <v>628355.51352661964</v>
+      </c>
+      <c r="L58" s="17">
+        <v>82774.843369345588</v>
+      </c>
+      <c r="M58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="N58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="O58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="P58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -22848,7 +23125,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25942,6 +26219,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="58" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-25998.161012664015</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-24252.015265919163</v>
+      </c>
+      <c r="G58" s="18">
+        <v>14907950.906946177</v>
+      </c>
+      <c r="H58" s="18">
+        <v>15981323.770331539</v>
+      </c>
+      <c r="I58" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J58" s="18">
+        <v>16482407.681704661</v>
+      </c>
+      <c r="K58" s="18">
+        <v>5594571.908223683</v>
+      </c>
+      <c r="L58" s="17">
+        <v>501083.91137312236</v>
+      </c>
+      <c r="M58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="N58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="O58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="P58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -25958,7 +26285,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29394,6 +29721,62 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="58" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="17">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="17">
+        <v>-3094.6848527484703</v>
+      </c>
+      <c r="H58" s="18">
+        <v>-2886.8328131172739</v>
+      </c>
+      <c r="I58" s="18">
+        <v>1990645.8030818715</v>
+      </c>
+      <c r="J58" s="18">
+        <v>2133972.3540597442</v>
+      </c>
+      <c r="K58" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L58" s="18">
+        <v>2175059.0316076181</v>
+      </c>
+      <c r="M58" s="18">
+        <v>855963.43993971287</v>
+      </c>
+      <c r="N58" s="17">
+        <v>41086.677547874053</v>
+      </c>
+      <c r="O58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="P58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="Q58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -29410,7 +29793,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -32688,6 +33071,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="58" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-21137.813820429725</v>
+      </c>
+      <c r="G58" s="18">
+        <v>1514526.7423422448</v>
+      </c>
+      <c r="H58" s="18">
+        <v>1623572.7082331136</v>
+      </c>
+      <c r="I58" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J58" s="18">
+        <v>1757214.9098912054</v>
+      </c>
+      <c r="K58" s="18">
+        <v>582403.11399565288</v>
+      </c>
+      <c r="L58" s="17">
+        <v>133642.20165809162</v>
+      </c>
+      <c r="M58" s="21">
+        <v>79.155674275563754</v>
+      </c>
+      <c r="N58" s="21">
+        <v>81.138653156326924</v>
+      </c>
+      <c r="O58" s="21">
+        <v>81.368329511252213</v>
+      </c>
+      <c r="P58" s="21">
+        <v>80.679300446476333</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -32704,7 +33140,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35496,6 +35932,50 @@
         <v>371112.60691969306</v>
       </c>
     </row>
+    <row r="58" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="17">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="17">
+        <v>-111127.31971233143</v>
+      </c>
+      <c r="H58" s="18">
+        <v>-103663.54192557483</v>
+      </c>
+      <c r="I58" s="18">
+        <v>12323772.532478964</v>
+      </c>
+      <c r="J58" s="18">
+        <v>13211084.483897679</v>
+      </c>
+      <c r="K58" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L58" s="18">
+        <v>13693324.410529703</v>
+      </c>
+      <c r="M58" s="18">
+        <v>5417684.417233428</v>
+      </c>
+      <c r="N58" s="17">
+        <v>482239.92663202446</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -35512,7 +35992,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37965,6 +38445,44 @@
         <v>628259.51158101915</v>
       </c>
     </row>
+    <row r="58" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="18">
+        <v>12659943.042425262</v>
+      </c>
+      <c r="H58" s="18">
+        <v>13571459.279536832</v>
+      </c>
+      <c r="I58" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J58" s="18">
+        <v>14329709.596181171</v>
+      </c>
+      <c r="K58" s="18">
+        <v>4968374.7784537468</v>
+      </c>
+      <c r="L58" s="17">
+        <v>758250.31664433924</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -755,6 +755,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -764,7 +767,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -931,6 +934,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -974,7 +980,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1142,6 +1148,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1151,7 +1160,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1319,6 +1328,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1729862.4147042707</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1734329.4800120019</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1361,7 +1373,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1529,6 +1541,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1538,7 +1553,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1706,6 +1721,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>571369.38522204687</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>575836.45052977814</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1727,11 +1745,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="564126848"/>
-        <c:axId val="564128384"/>
+        <c:axId val="483331072"/>
+        <c:axId val="483410688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="564126848"/>
+        <c:axId val="483331072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1774,14 +1792,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564128384"/>
+        <c:crossAx val="483410688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="564128384"/>
+        <c:axId val="483410688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1832,7 +1850,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="564126848"/>
+        <c:crossAx val="483331072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1993,7 +2011,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2161,6 +2179,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2180,8 +2201,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="530166912"/>
-        <c:axId val="530152832"/>
+        <c:axId val="378258560"/>
+        <c:axId val="378256768"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2206,7 +2227,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2374,6 +2395,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2383,7 +2407,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2551,6 +2575,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2572,11 +2599,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530149760"/>
-        <c:axId val="530151296"/>
+        <c:axId val="378253696"/>
+        <c:axId val="378255232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530149760"/>
+        <c:axId val="378253696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,14 +2646,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530151296"/>
+        <c:crossAx val="378255232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530151296"/>
+        <c:axId val="378255232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2677,12 +2704,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530149760"/>
+        <c:crossAx val="378253696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="530152832"/>
+        <c:axId val="378256768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2719,12 +2746,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530166912"/>
+        <c:crossAx val="378258560"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="530166912"/>
+        <c:axId val="378258560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2733,7 +2760,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="530152832"/>
+        <c:crossAx val="378256768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2883,7 +2910,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3051,6 +3078,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3060,7 +3090,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3227,6 +3257,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3270,7 +3303,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3438,6 +3471,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3447,7 +3483,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3615,6 +3651,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>13693324.410529703</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>13730295.986690177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3657,7 +3696,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3825,6 +3864,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3834,7 +3876,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4002,6 +4044,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5417684.417233428</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5454655.9933939017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4023,11 +4068,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="543072640"/>
-        <c:axId val="543074176"/>
+        <c:axId val="395252096"/>
+        <c:axId val="395253632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="543072640"/>
+        <c:axId val="395252096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4070,14 +4115,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543074176"/>
+        <c:crossAx val="395253632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="543074176"/>
+        <c:axId val="395253632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4128,7 +4173,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543072640"/>
+        <c:crossAx val="395252096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4289,7 +4334,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4457,6 +4502,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-111127.31971233143</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-56932.913434554059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4476,8 +4524,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="543774208"/>
-        <c:axId val="543772672"/>
+        <c:axId val="395286016"/>
+        <c:axId val="395284480"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4502,7 +4550,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4670,6 +4718,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4679,7 +4730,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4847,6 +4898,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4868,11 +4922,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="543765248"/>
-        <c:axId val="543766784"/>
+        <c:axId val="395277056"/>
+        <c:axId val="395278592"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="543765248"/>
+        <c:axId val="395277056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4915,14 +4969,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543766784"/>
+        <c:crossAx val="395278592"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="543766784"/>
+        <c:axId val="395278592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4973,12 +5027,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543765248"/>
+        <c:crossAx val="395277056"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="543772672"/>
+        <c:axId val="395284480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5015,12 +5069,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543774208"/>
+        <c:crossAx val="395286016"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="543774208"/>
+        <c:axId val="395286016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5029,7 +5083,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="543772672"/>
+        <c:crossAx val="395284480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5179,7 +5233,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5347,6 +5401,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5356,7 +5413,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5523,6 +5580,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5566,7 +5626,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5734,6 +5794,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5743,7 +5806,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5911,6 +5974,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>14329709.596181171</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14367689.690924622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5953,7 +6019,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6121,6 +6187,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6130,7 +6199,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6298,6 +6367,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4968374.7784537468</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5006354.8731971979</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6319,11 +6391,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556012288"/>
-        <c:axId val="556013824"/>
+        <c:axId val="395309824"/>
+        <c:axId val="395311360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556012288"/>
+        <c:axId val="395309824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6366,14 +6438,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556013824"/>
+        <c:crossAx val="395311360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556013824"/>
+        <c:axId val="395311360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6424,7 +6496,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556012288"/>
+        <c:crossAx val="395309824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6585,7 +6657,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6753,6 +6825,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6772,8 +6847,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="556058496"/>
-        <c:axId val="556056960"/>
+        <c:axId val="395597696"/>
+        <c:axId val="395596160"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6798,7 +6873,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6966,6 +7041,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6975,7 +7053,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7143,6 +7221,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7164,11 +7245,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556049536"/>
-        <c:axId val="556051072"/>
+        <c:axId val="395588736"/>
+        <c:axId val="395590272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556049536"/>
+        <c:axId val="395588736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7211,14 +7292,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556051072"/>
+        <c:crossAx val="395590272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556051072"/>
+        <c:axId val="395590272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7269,12 +7350,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556049536"/>
+        <c:crossAx val="395588736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="556056960"/>
+        <c:axId val="395596160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7311,12 +7392,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556058496"/>
+        <c:crossAx val="395597696"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="556058496"/>
+        <c:axId val="395597696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7325,7 +7406,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="556056960"/>
+        <c:crossAx val="395596160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7457,7 +7538,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7625,6 +7706,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7644,8 +7728,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="609222656"/>
-        <c:axId val="609200000"/>
+        <c:axId val="531184256"/>
+        <c:axId val="531182336"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7670,7 +7754,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7838,6 +7922,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7847,7 +7934,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8015,6 +8102,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8036,11 +8126,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="609114752"/>
-        <c:axId val="609198464"/>
+        <c:axId val="530805504"/>
+        <c:axId val="530807040"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="609114752"/>
+        <c:axId val="530805504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8083,14 +8173,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="609198464"/>
+        <c:crossAx val="530807040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="609198464"/>
+        <c:axId val="530807040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8141,12 +8231,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="609114752"/>
+        <c:crossAx val="530805504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="609200000"/>
+        <c:axId val="531182336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8183,12 +8273,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="609222656"/>
+        <c:crossAx val="531184256"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="609222656"/>
+        <c:axId val="531184256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8197,7 +8287,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="609200000"/>
+        <c:crossAx val="531182336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8347,7 +8437,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8515,6 +8605,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8524,7 +8617,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8691,6 +8784,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -8734,7 +8830,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8902,6 +8998,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8911,7 +9010,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9079,6 +9178,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1948247.1056262129</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1953467.680053948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9121,7 +9223,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9289,6 +9391,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9298,7 +9403,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9466,6 +9571,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>628355.51352661964</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>633576.08795435471</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9487,11 +9595,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662115840"/>
-        <c:axId val="662117376"/>
+        <c:axId val="537648128"/>
+        <c:axId val="623972736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662115840"/>
+        <c:axId val="537648128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9534,14 +9642,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662117376"/>
+        <c:crossAx val="623972736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662117376"/>
+        <c:axId val="623972736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9592,7 +9700,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662115840"/>
+        <c:crossAx val="537648128"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9774,7 +9882,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9942,6 +10050,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-4531.947395988238</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-4353.0431608345843</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9961,8 +10072,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529649024"/>
-        <c:axId val="529647488"/>
+        <c:axId val="76955008"/>
+        <c:axId val="76953472"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9987,7 +10098,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10155,6 +10266,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10164,7 +10278,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10332,6 +10446,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10353,11 +10470,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529640064"/>
-        <c:axId val="529645952"/>
+        <c:axId val="76946048"/>
+        <c:axId val="76951936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529640064"/>
+        <c:axId val="76946048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10400,14 +10517,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529645952"/>
+        <c:crossAx val="76951936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529645952"/>
+        <c:axId val="76951936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10458,12 +10575,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529640064"/>
+        <c:crossAx val="76946048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529647488"/>
+        <c:axId val="76953472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10500,12 +10617,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529649024"/>
+        <c:crossAx val="76955008"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529649024"/>
+        <c:axId val="76955008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10514,7 +10631,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529647488"/>
+        <c:crossAx val="76953472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10664,7 +10781,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10832,6 +10949,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10841,7 +10961,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11008,6 +11128,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11051,7 +11174,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11219,6 +11342,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11228,7 +11354,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11396,6 +11522,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>16482407.681704661</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>16527131.847206756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11438,7 +11567,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11606,6 +11735,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11615,7 +11747,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11783,6 +11915,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5594571.908223683</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5639296.0737257786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11804,11 +11939,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529668736"/>
-        <c:axId val="529674624"/>
+        <c:axId val="76970624"/>
+        <c:axId val="76972416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529668736"/>
+        <c:axId val="76970624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11851,14 +11986,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529674624"/>
+        <c:crossAx val="76972416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529674624"/>
+        <c:axId val="76972416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11909,7 +12044,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529668736"/>
+        <c:crossAx val="76970624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12091,7 +12226,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12259,6 +12394,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-25998.161012664015</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-23986.056658340185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12278,8 +12416,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529699584"/>
-        <c:axId val="529697792"/>
+        <c:axId val="81789696"/>
+        <c:axId val="76995584"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12304,7 +12442,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12472,6 +12610,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12481,7 +12622,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12649,6 +12790,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12670,11 +12814,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529694720"/>
-        <c:axId val="529696256"/>
+        <c:axId val="76992512"/>
+        <c:axId val="76994048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529694720"/>
+        <c:axId val="76992512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12717,14 +12861,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529696256"/>
+        <c:crossAx val="76994048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529696256"/>
+        <c:axId val="76994048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12775,12 +12919,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529694720"/>
+        <c:crossAx val="76992512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529697792"/>
+        <c:axId val="76995584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12817,12 +12961,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529699584"/>
+        <c:crossAx val="81789696"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529699584"/>
+        <c:axId val="81789696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12831,7 +12975,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529697792"/>
+        <c:crossAx val="76995584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12981,7 +13125,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13149,6 +13293,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13158,7 +13305,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13325,6 +13472,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13368,7 +13518,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13536,6 +13686,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13545,7 +13698,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13713,6 +13866,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>2175059.0316076181</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2181031.0107822744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13755,7 +13911,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13923,6 +14079,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13932,7 +14091,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14100,6 +14259,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>855963.43993971287</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>861935.4191143692</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14121,11 +14283,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530042880"/>
-        <c:axId val="530044416"/>
+        <c:axId val="81842176"/>
+        <c:axId val="81843712"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530042880"/>
+        <c:axId val="81842176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14168,14 +14330,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530044416"/>
+        <c:crossAx val="81843712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530044416"/>
+        <c:axId val="81843712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14226,7 +14388,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530042880"/>
+        <c:crossAx val="81842176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14387,7 +14549,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14555,6 +14717,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-3094.6848527484703</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-1585.4735386837842</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14574,8 +14739,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="530109568"/>
-        <c:axId val="530107776"/>
+        <c:axId val="378217600"/>
+        <c:axId val="378215808"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14600,7 +14765,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14768,6 +14933,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14777,7 +14945,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -14945,6 +15113,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14966,11 +15137,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530104704"/>
-        <c:axId val="530106240"/>
+        <c:axId val="378212736"/>
+        <c:axId val="378214272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530104704"/>
+        <c:axId val="378212736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15013,14 +15184,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530106240"/>
+        <c:crossAx val="378214272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530106240"/>
+        <c:axId val="378214272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15071,12 +15242,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530104704"/>
+        <c:crossAx val="378212736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="530107776"/>
+        <c:axId val="378215808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15113,12 +15284,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530109568"/>
+        <c:crossAx val="378217600"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="530109568"/>
+        <c:axId val="378217600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15127,7 +15298,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="530107776"/>
+        <c:crossAx val="378215808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15277,7 +15448,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15445,6 +15616,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15454,7 +15628,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15621,6 +15795,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -15664,7 +15841,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15832,6 +16009,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15841,7 +16021,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16009,6 +16189,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1757214.9098912054</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1761758.5218942678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16051,7 +16234,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16219,6 +16402,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16228,7 +16414,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16396,6 +16582,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>582403.11399565288</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>586946.72599871526</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16417,11 +16606,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530137088"/>
-        <c:axId val="530138624"/>
+        <c:axId val="378236928"/>
+        <c:axId val="378238464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530137088"/>
+        <c:axId val="378236928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16464,14 +16653,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530138624"/>
+        <c:crossAx val="378238464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530138624"/>
+        <c:axId val="378238464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16522,7 +16711,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530137088"/>
+        <c:crossAx val="378236928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17458,7 +17647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -19949,6 +20138,44 @@
         <v>133642.20165809162</v>
       </c>
     </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="32">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="31">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="29">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="29">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F59" s="30">
+        <v>-20246.711477892542</v>
+      </c>
+      <c r="G59" s="30">
+        <v>1468764.6441986805</v>
+      </c>
+      <c r="H59" s="30">
+        <v>1578922.0625497375</v>
+      </c>
+      <c r="I59" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J59" s="30">
+        <v>1734329.4800120019</v>
+      </c>
+      <c r="K59" s="30">
+        <v>575836.45052977814</v>
+      </c>
+      <c r="L59" s="29">
+        <v>155407.41746226454</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -19965,7 +20192,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23109,6 +23336,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="59" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-4353.0431608345843</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-4049.342295578509</v>
+      </c>
+      <c r="G59" s="18">
+        <v>1736129.9634778046</v>
+      </c>
+      <c r="H59" s="18">
+        <v>1866339.7935237677</v>
+      </c>
+      <c r="I59" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J59" s="18">
+        <v>1953467.680053948</v>
+      </c>
+      <c r="K59" s="18">
+        <v>633576.08795435471</v>
+      </c>
+      <c r="L59" s="17">
+        <v>87127.886530180171</v>
+      </c>
+      <c r="M59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="N59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="O59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="P59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23125,7 +23402,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26269,6 +26546,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="59" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-23986.056658340185</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-22312.609855248407</v>
+      </c>
+      <c r="G59" s="18">
+        <v>14885638.297090929</v>
+      </c>
+      <c r="H59" s="18">
+        <v>16002061.879175294</v>
+      </c>
+      <c r="I59" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J59" s="18">
+        <v>16527131.847206756</v>
+      </c>
+      <c r="K59" s="18">
+        <v>5639296.0737257786</v>
+      </c>
+      <c r="L59" s="17">
+        <v>525069.96803146251</v>
+      </c>
+      <c r="M59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="N59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="O59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="P59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -26285,7 +26612,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29777,6 +30104,62 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="59" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="17">
+        <v>-1585.4735386837842</v>
+      </c>
+      <c r="H59" s="18">
+        <v>-1474.8590403321161</v>
+      </c>
+      <c r="I59" s="18">
+        <v>1989170.9440415394</v>
+      </c>
+      <c r="J59" s="18">
+        <v>2138358.8596957168</v>
+      </c>
+      <c r="K59" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L59" s="18">
+        <v>2181031.0107822744</v>
+      </c>
+      <c r="M59" s="18">
+        <v>861935.4191143692</v>
+      </c>
+      <c r="N59" s="17">
+        <v>42672.151086557838</v>
+      </c>
+      <c r="O59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="P59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="Q59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -29793,7 +30176,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -33124,6 +33507,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-20246.711477892542</v>
+      </c>
+      <c r="G59" s="18">
+        <v>1494280.0308643524</v>
+      </c>
+      <c r="H59" s="18">
+        <v>1606351.1044320031</v>
+      </c>
+      <c r="I59" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J59" s="18">
+        <v>1761758.5218942678</v>
+      </c>
+      <c r="K59" s="18">
+        <v>586946.72599871526</v>
+      </c>
+      <c r="L59" s="17">
+        <v>155407.41746226454</v>
+      </c>
+      <c r="M59" s="21">
+        <v>79.947236522705992</v>
+      </c>
+      <c r="N59" s="21">
+        <v>80.74151427845328</v>
+      </c>
+      <c r="O59" s="21">
+        <v>81.15939110031924</v>
+      </c>
+      <c r="P59" s="21">
+        <v>79.905760634721361</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -33140,7 +33576,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35976,6 +36412,50 @@
         <v>482239.92663202446</v>
       </c>
     </row>
+    <row r="59" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="17">
+        <v>-56932.913434554059</v>
+      </c>
+      <c r="H59" s="18">
+        <v>-52960.847357380524</v>
+      </c>
+      <c r="I59" s="18">
+        <v>12270811.685121583</v>
+      </c>
+      <c r="J59" s="18">
+        <v>13191123.146623598</v>
+      </c>
+      <c r="K59" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L59" s="18">
+        <v>13730295.986690177</v>
+      </c>
+      <c r="M59" s="18">
+        <v>5454655.9933939017</v>
+      </c>
+      <c r="N59" s="17">
+        <v>539172.84006657847</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -35992,7 +36472,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -38483,6 +38963,44 @@
         <v>758250.31664433924</v>
       </c>
     </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="18">
+        <v>12548379.99314902</v>
+      </c>
+      <c r="H59" s="18">
+        <v>13489509.090988582</v>
+      </c>
+      <c r="I59" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J59" s="18">
+        <v>14367689.690924622</v>
+      </c>
+      <c r="K59" s="18">
+        <v>5006354.8731971979</v>
+      </c>
+      <c r="L59" s="17">
+        <v>878180.59993604012</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -758,6 +758,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -767,7 +770,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -937,6 +940,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -980,7 +986,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1151,6 +1157,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1160,7 +1169,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1331,6 +1340,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1734329.4800120019</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1694672.7323658499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1373,7 +1385,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1544,6 +1556,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1553,7 +1568,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1724,6 +1739,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>575836.45052977814</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>536179.7028836261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1745,11 +1763,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483331072"/>
-        <c:axId val="483410688"/>
+        <c:axId val="427817600"/>
+        <c:axId val="428208512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483331072"/>
+        <c:axId val="427817600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1792,14 +1810,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483410688"/>
+        <c:crossAx val="428208512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483410688"/>
+        <c:axId val="428208512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1850,7 +1868,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="483331072"/>
+        <c:crossAx val="427817600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2011,7 +2029,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2182,6 +2200,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2201,8 +2222,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="378258560"/>
-        <c:axId val="378256768"/>
+        <c:axId val="113933312"/>
+        <c:axId val="113931776"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2227,7 +2248,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2398,6 +2419,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2407,7 +2431,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2578,6 +2602,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2599,11 +2626,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="378253696"/>
-        <c:axId val="378255232"/>
+        <c:axId val="113928448"/>
+        <c:axId val="113930240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="378253696"/>
+        <c:axId val="113928448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2646,14 +2673,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378255232"/>
+        <c:crossAx val="113930240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="378255232"/>
+        <c:axId val="113930240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2704,12 +2731,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378253696"/>
+        <c:crossAx val="113928448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="378256768"/>
+        <c:axId val="113931776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2746,12 +2773,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378258560"/>
+        <c:crossAx val="113933312"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="378258560"/>
+        <c:axId val="113933312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2760,7 +2787,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="378256768"/>
+        <c:crossAx val="113931776"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2910,7 +2937,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3081,6 +3108,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3090,7 +3120,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3260,6 +3290,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3303,7 +3336,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3474,6 +3507,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3483,7 +3519,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3654,6 +3690,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>13730295.986690177</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13398983.216919765</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3696,7 +3735,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3867,6 +3906,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3876,7 +3918,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4047,6 +4089,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5454655.9933939017</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5123343.22362349</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4068,11 +4113,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="395252096"/>
-        <c:axId val="395253632"/>
+        <c:axId val="428165376"/>
+        <c:axId val="428171264"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="395252096"/>
+        <c:axId val="428165376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4115,14 +4160,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395253632"/>
+        <c:crossAx val="428171264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395253632"/>
+        <c:axId val="428171264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4173,7 +4218,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395252096"/>
+        <c:crossAx val="428165376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4334,7 +4379,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4505,6 +4550,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-56932.913434554059</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-37743.814809844756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4524,8 +4572,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="395286016"/>
-        <c:axId val="395284480"/>
+        <c:axId val="428215680"/>
+        <c:axId val="428214144"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4550,7 +4598,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4721,6 +4769,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4730,7 +4781,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4901,6 +4952,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4922,11 +4976,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="395277056"/>
-        <c:axId val="395278592"/>
+        <c:axId val="428194432"/>
+        <c:axId val="428212608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="395277056"/>
+        <c:axId val="428194432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4969,14 +5023,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395278592"/>
+        <c:crossAx val="428212608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395278592"/>
+        <c:axId val="428212608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5027,12 +5081,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395277056"/>
+        <c:crossAx val="428194432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="395284480"/>
+        <c:axId val="428214144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5069,12 +5123,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395286016"/>
+        <c:crossAx val="428215680"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="395286016"/>
+        <c:axId val="428215680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5083,7 +5137,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="395284480"/>
+        <c:crossAx val="428214144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5233,7 +5287,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5404,6 +5458,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5413,7 +5470,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5583,6 +5640,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5626,7 +5686,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5797,6 +5857,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5806,7 +5869,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5977,6 +6040,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14367689.690924622</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14028882.557513656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6019,7 +6085,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6190,6 +6256,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6199,7 +6268,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6370,6 +6439,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5006354.8731971979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4667547.7397862319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6391,11 +6463,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="395309824"/>
-        <c:axId val="395311360"/>
+        <c:axId val="432679552"/>
+        <c:axId val="432697728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="395309824"/>
+        <c:axId val="432679552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6438,14 +6510,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395311360"/>
+        <c:crossAx val="432697728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395311360"/>
+        <c:axId val="432697728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6496,7 +6568,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395309824"/>
+        <c:crossAx val="432679552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6657,7 +6729,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6828,6 +6900,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6847,8 +6922,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="395597696"/>
-        <c:axId val="395596160"/>
+        <c:axId val="432726016"/>
+        <c:axId val="432716032"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6873,7 +6948,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7044,6 +7119,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7053,7 +7131,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7224,6 +7302,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7245,11 +7326,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="395588736"/>
-        <c:axId val="395590272"/>
+        <c:axId val="432708608"/>
+        <c:axId val="432714496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="395588736"/>
+        <c:axId val="432708608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7292,14 +7373,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395590272"/>
+        <c:crossAx val="432714496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395590272"/>
+        <c:axId val="432714496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7350,12 +7431,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395588736"/>
+        <c:crossAx val="432708608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="395596160"/>
+        <c:axId val="432716032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7392,12 +7473,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395597696"/>
+        <c:crossAx val="432726016"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="395597696"/>
+        <c:axId val="432726016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7406,7 +7487,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="395596160"/>
+        <c:crossAx val="432716032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7538,7 +7619,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7709,6 +7790,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7728,8 +7812,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="531184256"/>
-        <c:axId val="531182336"/>
+        <c:axId val="525891456"/>
+        <c:axId val="525889536"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7754,7 +7838,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7925,6 +8009,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7934,7 +8021,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8105,6 +8192,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8126,11 +8216,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530805504"/>
-        <c:axId val="530807040"/>
+        <c:axId val="521322880"/>
+        <c:axId val="521324800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530805504"/>
+        <c:axId val="521322880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8173,14 +8263,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530807040"/>
+        <c:crossAx val="521324800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530807040"/>
+        <c:axId val="521324800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8231,12 +8321,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530805504"/>
+        <c:crossAx val="521322880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="531182336"/>
+        <c:axId val="525889536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8273,12 +8363,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531184256"/>
+        <c:crossAx val="525891456"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="531184256"/>
+        <c:axId val="525891456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8287,7 +8377,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="531182336"/>
+        <c:crossAx val="525889536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8437,7 +8527,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8608,6 +8698,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8617,7 +8710,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8787,6 +8880,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -8830,7 +8926,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9001,6 +9097,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9010,7 +9109,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9181,6 +9280,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1953467.680053948</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1906592.0501737606</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9223,7 +9325,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9394,6 +9496,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9403,7 +9508,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9574,6 +9679,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>633576.08795435471</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>586700.45807416737</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9595,11 +9703,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="537648128"/>
-        <c:axId val="623972736"/>
+        <c:axId val="526199424"/>
+        <c:axId val="526430976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="537648128"/>
+        <c:axId val="526199424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9642,14 +9750,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623972736"/>
+        <c:crossAx val="526430976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623972736"/>
+        <c:axId val="526430976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9700,7 +9808,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="537648128"/>
+        <c:crossAx val="526199424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9882,7 +9990,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10053,6 +10161,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-4353.0431608345843</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-3486.2836718054768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10072,8 +10183,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="76955008"/>
-        <c:axId val="76953472"/>
+        <c:axId val="78947840"/>
+        <c:axId val="78946304"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10098,7 +10209,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10269,6 +10380,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10278,7 +10392,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10449,6 +10563,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10470,11 +10587,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="76946048"/>
-        <c:axId val="76951936"/>
+        <c:axId val="78938880"/>
+        <c:axId val="78940416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="76946048"/>
+        <c:axId val="78938880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10517,14 +10634,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76951936"/>
+        <c:crossAx val="78940416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="76951936"/>
+        <c:axId val="78940416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10575,12 +10692,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76946048"/>
+        <c:crossAx val="78938880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="76953472"/>
+        <c:axId val="78946304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10617,12 +10734,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76955008"/>
+        <c:crossAx val="78947840"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="76955008"/>
+        <c:axId val="78947840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10631,7 +10748,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="76953472"/>
+        <c:crossAx val="78946304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10781,7 +10898,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10952,6 +11069,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10961,7 +11081,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11131,6 +11251,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11174,7 +11297,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11345,6 +11468,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11354,7 +11480,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11525,6 +11651,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>16527131.847206756</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>16125218.576873584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11567,7 +11696,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11738,6 +11867,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11747,7 +11879,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11918,6 +12050,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5639296.0737257786</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5237382.8033926059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11939,11 +12074,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="76970624"/>
-        <c:axId val="76972416"/>
+        <c:axId val="79024896"/>
+        <c:axId val="79026432"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="76970624"/>
+        <c:axId val="79024896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11986,14 +12121,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76972416"/>
+        <c:crossAx val="79026432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="76972416"/>
+        <c:axId val="79026432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12044,7 +12179,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76970624"/>
+        <c:crossAx val="79024896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12226,7 +12361,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12397,6 +12532,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-23986.056658340185</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-15385.030177591741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12416,8 +12554,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="81789696"/>
-        <c:axId val="76995584"/>
+        <c:axId val="79849728"/>
+        <c:axId val="79848192"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12442,7 +12580,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12613,6 +12751,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12622,7 +12763,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12793,6 +12934,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12814,11 +12958,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="76992512"/>
-        <c:axId val="76994048"/>
+        <c:axId val="79840768"/>
+        <c:axId val="79842304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="76992512"/>
+        <c:axId val="79840768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12861,14 +13005,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76994048"/>
+        <c:crossAx val="79842304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="76994048"/>
+        <c:axId val="79842304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12919,12 +13063,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76992512"/>
+        <c:crossAx val="79840768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="76995584"/>
+        <c:axId val="79848192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12961,12 +13105,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81789696"/>
+        <c:crossAx val="79849728"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="81789696"/>
+        <c:axId val="79849728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12975,7 +13119,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="76995584"/>
+        <c:crossAx val="79848192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13125,7 +13269,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13296,6 +13440,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13305,7 +13452,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13475,6 +13622,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13518,7 +13668,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13689,6 +13839,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13698,7 +13851,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13869,6 +14022,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>2181031.0107822744</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2127323.2568106027</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13911,7 +14067,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14082,6 +14238,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14091,7 +14250,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14262,6 +14421,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>861935.4191143692</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>808227.66514269751</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14283,11 +14445,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="81842176"/>
-        <c:axId val="81843712"/>
+        <c:axId val="80020992"/>
+        <c:axId val="80022528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="81842176"/>
+        <c:axId val="80020992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14330,14 +14492,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81843712"/>
+        <c:crossAx val="80022528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81843712"/>
+        <c:axId val="80022528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14388,7 +14550,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81842176"/>
+        <c:crossAx val="80020992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14549,7 +14711,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14720,6 +14882,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-1585.4735386837842</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-1051.0935769830185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14739,8 +14904,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="378217600"/>
-        <c:axId val="378215808"/>
+        <c:axId val="80067200"/>
+        <c:axId val="80065664"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14765,7 +14930,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14936,6 +15101,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14945,7 +15113,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15116,6 +15284,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15137,11 +15308,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="378212736"/>
-        <c:axId val="378214272"/>
+        <c:axId val="80062336"/>
+        <c:axId val="80063872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="378212736"/>
+        <c:axId val="80062336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15184,14 +15355,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378214272"/>
+        <c:crossAx val="80063872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="378214272"/>
+        <c:axId val="80063872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15242,12 +15413,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378212736"/>
+        <c:crossAx val="80062336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="378215808"/>
+        <c:axId val="80065664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15284,12 +15455,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378217600"/>
+        <c:crossAx val="80067200"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="378217600"/>
+        <c:axId val="80067200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15298,7 +15469,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="378215808"/>
+        <c:crossAx val="80065664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15448,7 +15619,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15619,6 +15790,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15628,7 +15802,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15798,6 +15972,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -15841,7 +16018,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16012,6 +16189,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16021,7 +16201,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16192,6 +16372,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1761758.5218942678</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1721412.8570318066</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16234,7 +16417,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16405,6 +16588,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16414,7 +16600,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16585,6 +16771,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>586946.72599871526</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>546601.06113625411</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16606,11 +16795,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="378236928"/>
-        <c:axId val="378238464"/>
+        <c:axId val="103315328"/>
+        <c:axId val="103316864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="378236928"/>
+        <c:axId val="103315328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16653,14 +16842,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378238464"/>
+        <c:crossAx val="103316864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="378238464"/>
+        <c:axId val="103316864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16711,7 +16900,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378236928"/>
+        <c:crossAx val="103315328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17647,7 +17836,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -20176,6 +20365,44 @@
         <v>155407.41746226454</v>
       </c>
     </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="32">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="31">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="29">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="29">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F60" s="30">
+        <v>-16633.033133458779</v>
+      </c>
+      <c r="G60" s="30">
+        <v>1452131.6110652217</v>
+      </c>
+      <c r="H60" s="30">
+        <v>1521833.896544558</v>
+      </c>
+      <c r="I60" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J60" s="30">
+        <v>1694672.7323658499</v>
+      </c>
+      <c r="K60" s="30">
+        <v>536179.7028836261</v>
+      </c>
+      <c r="L60" s="29">
+        <v>172838.83582129193</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20192,7 +20419,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23386,6 +23613,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="60" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-3486.2836718054768</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-3326.6066266917564</v>
+      </c>
+      <c r="G60" s="18">
+        <v>1732803.3568511128</v>
+      </c>
+      <c r="H60" s="18">
+        <v>1815977.879971775</v>
+      </c>
+      <c r="I60" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J60" s="18">
+        <v>1906592.0501737606</v>
+      </c>
+      <c r="K60" s="18">
+        <v>586700.45807416737</v>
+      </c>
+      <c r="L60" s="17">
+        <v>90614.170201985646</v>
+      </c>
+      <c r="M60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="N60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="O60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23402,7 +23679,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26596,6 +26873,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="60" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-15385.030177591741</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-14680.372614120717</v>
+      </c>
+      <c r="G60" s="18">
+        <v>14870957.924476808</v>
+      </c>
+      <c r="H60" s="18">
+        <v>15584763.57866453</v>
+      </c>
+      <c r="I60" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J60" s="18">
+        <v>16125218.576873584</v>
+      </c>
+      <c r="K60" s="18">
+        <v>5237382.8033926059</v>
+      </c>
+      <c r="L60" s="17">
+        <v>540454.99820905423</v>
+      </c>
+      <c r="M60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="N60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="O60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="P60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -26612,7 +26939,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30160,6 +30487,62 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="60" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="17">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="17">
+        <v>-1051.0935769830185</v>
+      </c>
+      <c r="H60" s="18">
+        <v>-1002.9519074258362</v>
+      </c>
+      <c r="I60" s="18">
+        <v>1988167.9921341136</v>
+      </c>
+      <c r="J60" s="18">
+        <v>2083600.0121470618</v>
+      </c>
+      <c r="K60" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L60" s="18">
+        <v>2127323.2568106027</v>
+      </c>
+      <c r="M60" s="18">
+        <v>808227.66514269751</v>
+      </c>
+      <c r="N60" s="17">
+        <v>43723.244663540856</v>
+      </c>
+      <c r="O60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="P60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="Q60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -30176,7 +30559,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -33560,6 +33943,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-16633.033133458779</v>
+      </c>
+      <c r="G60" s="18">
+        <v>1477646.9977308935</v>
+      </c>
+      <c r="H60" s="18">
+        <v>1548574.0212105147</v>
+      </c>
+      <c r="I60" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J60" s="18">
+        <v>1721412.8570318066</v>
+      </c>
+      <c r="K60" s="18">
+        <v>546601.06113625411</v>
+      </c>
+      <c r="L60" s="17">
+        <v>172838.83582129193</v>
+      </c>
+      <c r="M60" s="21">
+        <v>70.655258802170835</v>
+      </c>
+      <c r="N60" s="21">
+        <v>77.37942911969246</v>
+      </c>
+      <c r="O60" s="21">
+        <v>79.899403773443638</v>
+      </c>
+      <c r="P60" s="21">
+        <v>72.339479812190092</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -33576,7 +34012,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36456,6 +36892,50 @@
         <v>539172.84006657847</v>
       </c>
     </row>
+    <row r="60" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="17">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="17">
+        <v>-37743.814809844756</v>
+      </c>
+      <c r="H60" s="18">
+        <v>-36015.091221200484</v>
+      </c>
+      <c r="I60" s="18">
+        <v>12234796.593900383</v>
+      </c>
+      <c r="J60" s="18">
+        <v>12822066.562043341</v>
+      </c>
+      <c r="K60" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L60" s="18">
+        <v>13398983.216919765</v>
+      </c>
+      <c r="M60" s="18">
+        <v>5123343.22362349</v>
+      </c>
+      <c r="N60" s="17">
+        <v>576916.65487642318</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -36472,7 +36952,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -39001,6 +39481,44 @@
         <v>878180.59993604012</v>
       </c>
     </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="18">
+        <v>12474978.130078416</v>
+      </c>
+      <c r="H60" s="18">
+        <v>13073776.806689657</v>
+      </c>
+      <c r="I60" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J60" s="18">
+        <v>14028882.557513656</v>
+      </c>
+      <c r="K60" s="18">
+        <v>4667547.7397862319</v>
+      </c>
+      <c r="L60" s="17">
+        <v>955105.75082399882</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -761,6 +761,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -770,7 +773,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -943,6 +946,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -986,7 +992,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1160,6 +1166,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1169,7 +1178,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1343,6 +1352,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1694672.7323658499</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1881997.8085183678</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1385,7 +1397,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1559,6 +1571,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1568,7 +1583,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1742,6 +1757,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>536179.7028836261</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>723504.77903614403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1763,11 +1781,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="427817600"/>
-        <c:axId val="428208512"/>
+        <c:axId val="643962752"/>
+        <c:axId val="643964288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="427817600"/>
+        <c:axId val="643962752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1810,14 +1828,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="428208512"/>
+        <c:crossAx val="643964288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="428208512"/>
+        <c:axId val="643964288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1868,7 +1886,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427817600"/>
+        <c:crossAx val="643962752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2029,7 +2047,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2203,6 +2221,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2222,8 +2243,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="113933312"/>
-        <c:axId val="113931776"/>
+        <c:axId val="479033600"/>
+        <c:axId val="479032064"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2248,7 +2269,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2422,6 +2443,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2431,7 +2455,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2605,6 +2629,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2626,11 +2653,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="113928448"/>
-        <c:axId val="113930240"/>
+        <c:axId val="479024640"/>
+        <c:axId val="479026176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="113928448"/>
+        <c:axId val="479024640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2673,14 +2700,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="113930240"/>
+        <c:crossAx val="479026176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="113930240"/>
+        <c:axId val="479026176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2731,12 +2758,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="113928448"/>
+        <c:crossAx val="479024640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="113931776"/>
+        <c:axId val="479032064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2773,12 +2800,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="113933312"/>
+        <c:crossAx val="479033600"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="113933312"/>
+        <c:axId val="479033600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2787,7 +2814,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="113931776"/>
+        <c:crossAx val="479032064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2937,7 +2964,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3111,6 +3138,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3120,7 +3150,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3293,6 +3323,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3336,7 +3369,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3510,6 +3543,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3519,7 +3555,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3693,6 +3729,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>13398983.216919765</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>14977272.805961713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3735,7 +3774,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3909,6 +3948,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3918,7 +3960,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4092,6 +4134,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5123343.22362349</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6701632.8126654383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4113,11 +4158,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="428165376"/>
-        <c:axId val="428171264"/>
+        <c:axId val="479065600"/>
+        <c:axId val="479067136"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="428165376"/>
+        <c:axId val="479065600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4160,14 +4205,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="428171264"/>
+        <c:crossAx val="479067136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="428171264"/>
+        <c:axId val="479067136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4218,7 +4263,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="428165376"/>
+        <c:crossAx val="479065600"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4379,7 +4424,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4553,6 +4598,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-37743.814809844756</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-102248.30313182416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4572,8 +4620,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="428215680"/>
-        <c:axId val="428214144"/>
+        <c:axId val="481208960"/>
+        <c:axId val="481207424"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4598,7 +4646,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4772,6 +4820,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4781,7 +4832,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4955,6 +5006,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4976,11 +5030,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="428194432"/>
-        <c:axId val="428212608"/>
+        <c:axId val="481200000"/>
+        <c:axId val="481201536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="428194432"/>
+        <c:axId val="481200000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5023,14 +5077,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="428212608"/>
+        <c:crossAx val="481201536"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="428212608"/>
+        <c:axId val="481201536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5081,12 +5135,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="428194432"/>
+        <c:crossAx val="481200000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="428214144"/>
+        <c:axId val="481207424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5123,12 +5177,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="428215680"/>
+        <c:crossAx val="481208960"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="428215680"/>
+        <c:axId val="481208960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5137,7 +5191,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="428214144"/>
+        <c:crossAx val="481207424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5287,7 +5341,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5461,6 +5515,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5470,7 +5527,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5643,6 +5700,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5686,7 +5746,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5860,6 +5920,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5869,7 +5932,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6043,6 +6106,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14028882.557513656</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15638155.580985475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6085,7 +6151,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6259,6 +6325,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6268,7 +6337,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6442,6 +6511,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4667547.7397862319</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6276820.7632580511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6463,11 +6535,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="432679552"/>
-        <c:axId val="432697728"/>
+        <c:axId val="481355648"/>
+        <c:axId val="481357184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="432679552"/>
+        <c:axId val="481355648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6510,14 +6582,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432697728"/>
+        <c:crossAx val="481357184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="432697728"/>
+        <c:axId val="481357184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6568,7 +6640,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432679552"/>
+        <c:crossAx val="481355648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6729,7 +6801,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6903,6 +6975,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6922,8 +6997,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="432726016"/>
-        <c:axId val="432716032"/>
+        <c:axId val="481553408"/>
+        <c:axId val="481551872"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6948,7 +7023,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7122,6 +7197,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7131,7 +7209,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7305,6 +7383,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7326,11 +7407,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="432708608"/>
-        <c:axId val="432714496"/>
+        <c:axId val="481540352"/>
+        <c:axId val="481550336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="432708608"/>
+        <c:axId val="481540352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7373,14 +7454,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432714496"/>
+        <c:crossAx val="481550336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="432714496"/>
+        <c:axId val="481550336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7431,12 +7512,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432708608"/>
+        <c:crossAx val="481540352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="432716032"/>
+        <c:axId val="481551872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7473,12 +7554,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="432726016"/>
+        <c:crossAx val="481553408"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="432726016"/>
+        <c:axId val="481553408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7487,7 +7568,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="432716032"/>
+        <c:crossAx val="481551872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7619,7 +7700,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7793,6 +7874,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7812,8 +7896,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="525891456"/>
-        <c:axId val="525889536"/>
+        <c:axId val="458522624"/>
+        <c:axId val="458520832"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7838,7 +7922,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8012,6 +8096,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8021,7 +8108,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8195,6 +8282,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8216,11 +8306,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521322880"/>
-        <c:axId val="521324800"/>
+        <c:axId val="458513408"/>
+        <c:axId val="458519296"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521322880"/>
+        <c:axId val="458513408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8263,14 +8353,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521324800"/>
+        <c:crossAx val="458519296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521324800"/>
+        <c:axId val="458519296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8321,12 +8411,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521322880"/>
+        <c:crossAx val="458513408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="525889536"/>
+        <c:axId val="458520832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8363,12 +8453,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="525891456"/>
+        <c:crossAx val="458522624"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="525891456"/>
+        <c:axId val="458522624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8377,7 +8467,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="525889536"/>
+        <c:crossAx val="458520832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8527,7 +8617,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8701,6 +8791,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8710,7 +8803,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8883,6 +8976,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -8926,7 +9022,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9100,6 +9196,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9109,7 +9208,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9283,6 +9382,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1906592.0501737606</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2130123.8005371881</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9325,7 +9427,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9499,6 +9601,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9508,7 +9613,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9682,6 +9787,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>586700.45807416737</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>810232.20843759482</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9703,11 +9811,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526199424"/>
-        <c:axId val="526430976"/>
+        <c:axId val="458537984"/>
+        <c:axId val="458547968"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526199424"/>
+        <c:axId val="458537984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9750,14 +9858,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526430976"/>
+        <c:crossAx val="458547968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526430976"/>
+        <c:axId val="458547968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9808,7 +9916,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526199424"/>
+        <c:crossAx val="458537984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9990,7 +10098,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10164,6 +10272,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-3486.2836718054768</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-6554.9847565695836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10183,8 +10294,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="78947840"/>
-        <c:axId val="78946304"/>
+        <c:axId val="459490048"/>
+        <c:axId val="459484160"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10209,7 +10320,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10383,6 +10494,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10392,7 +10506,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10566,6 +10680,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10587,11 +10704,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="78938880"/>
-        <c:axId val="78940416"/>
+        <c:axId val="459481088"/>
+        <c:axId val="459482624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="78938880"/>
+        <c:axId val="459481088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10634,14 +10751,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78940416"/>
+        <c:crossAx val="459482624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="78940416"/>
+        <c:axId val="459482624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10692,12 +10809,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78938880"/>
+        <c:crossAx val="459481088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="78946304"/>
+        <c:axId val="459484160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10734,12 +10851,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78947840"/>
+        <c:crossAx val="459490048"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="78947840"/>
+        <c:axId val="459490048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10748,7 +10865,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="78946304"/>
+        <c:crossAx val="459484160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10898,7 +11015,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11072,6 +11189,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11081,7 +11201,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11254,6 +11374,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11297,7 +11420,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11471,6 +11594,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11480,7 +11606,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11654,6 +11780,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>16125218.576873584</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18043573.156056687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11696,7 +11825,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11870,6 +11999,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11879,7 +12011,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12053,6 +12185,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5237382.8033926059</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7155737.3825757094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12074,11 +12209,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79024896"/>
-        <c:axId val="79026432"/>
+        <c:axId val="460894208"/>
+        <c:axId val="460895744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79024896"/>
+        <c:axId val="460894208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12121,14 +12256,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79026432"/>
+        <c:crossAx val="460895744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79026432"/>
+        <c:axId val="460895744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12179,7 +12314,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79024896"/>
+        <c:crossAx val="460894208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12361,7 +12496,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12535,6 +12670,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-15385.030177591741</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-54389.65209982227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12554,8 +12692,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="79849728"/>
-        <c:axId val="79848192"/>
+        <c:axId val="478746496"/>
+        <c:axId val="478744960"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12580,7 +12718,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12754,6 +12892,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12763,7 +12904,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12937,6 +13078,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12958,11 +13102,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79840768"/>
-        <c:axId val="79842304"/>
+        <c:axId val="467010688"/>
+        <c:axId val="467012224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79840768"/>
+        <c:axId val="467010688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13005,14 +13149,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79842304"/>
+        <c:crossAx val="467012224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79842304"/>
+        <c:axId val="467012224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13063,12 +13207,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79840768"/>
+        <c:crossAx val="467010688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="79848192"/>
+        <c:axId val="478744960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13105,12 +13249,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79849728"/>
+        <c:crossAx val="478746496"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="79849728"/>
+        <c:axId val="478746496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13119,7 +13263,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="79848192"/>
+        <c:crossAx val="478744960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13269,7 +13413,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13443,6 +13587,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13452,7 +13599,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13625,6 +13772,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13668,7 +13818,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13842,6 +13992,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13851,7 +14004,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14025,6 +14178,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>2127323.2568106027</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2383797.0624165004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14067,7 +14223,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14241,6 +14397,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14250,7 +14409,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14424,6 +14583,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>808227.66514269751</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1064701.4707485952</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14445,11 +14607,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80020992"/>
-        <c:axId val="80022528"/>
+        <c:axId val="478778112"/>
+        <c:axId val="478779648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80020992"/>
+        <c:axId val="478778112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14492,14 +14654,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80022528"/>
+        <c:crossAx val="478779648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80022528"/>
+        <c:axId val="478779648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14550,7 +14712,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80020992"/>
+        <c:crossAx val="478778112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14711,7 +14873,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14885,6 +15047,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-1051.0935769830185</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-2847.4210998735844</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14904,8 +15069,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="80067200"/>
-        <c:axId val="80065664"/>
+        <c:axId val="478926720"/>
+        <c:axId val="478925184"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14930,7 +15095,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15104,6 +15269,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15113,7 +15281,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15287,6 +15455,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15308,11 +15479,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80062336"/>
-        <c:axId val="80063872"/>
+        <c:axId val="478889088"/>
+        <c:axId val="478890624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80062336"/>
+        <c:axId val="478889088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15355,14 +15526,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80063872"/>
+        <c:crossAx val="478890624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80063872"/>
+        <c:axId val="478890624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15413,12 +15584,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80062336"/>
+        <c:crossAx val="478889088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="80065664"/>
+        <c:axId val="478925184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15455,12 +15626,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80067200"/>
+        <c:crossAx val="478926720"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="80067200"/>
+        <c:axId val="478926720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15469,7 +15640,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="80065664"/>
+        <c:crossAx val="478925184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15619,7 +15790,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15793,6 +15964,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15802,7 +15976,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15975,6 +16149,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16018,7 +16195,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16192,6 +16369,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16201,7 +16381,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16375,6 +16555,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1721412.8570318066</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1912029.4197918652</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16417,7 +16600,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16591,6 +16774,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16600,7 +16786,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16774,6 +16960,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>546601.06113625411</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>737217.62389631267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16795,11 +16984,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="103315328"/>
-        <c:axId val="103316864"/>
+        <c:axId val="478995584"/>
+        <c:axId val="478997120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="103315328"/>
+        <c:axId val="478995584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16842,14 +17031,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103316864"/>
+        <c:crossAx val="478997120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103316864"/>
+        <c:axId val="478997120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16900,7 +17089,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103315328"/>
+        <c:crossAx val="478995584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17836,7 +18025,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -20403,6 +20592,44 @@
         <v>172838.83582129193</v>
       </c>
     </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="32">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="31">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="29">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="29">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F61" s="30">
+        <v>-27846.153362916037</v>
+      </c>
+      <c r="G61" s="30">
+        <v>1424285.4577023056</v>
+      </c>
+      <c r="H61" s="30">
+        <v>1676384.0489142279</v>
+      </c>
+      <c r="I61" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J61" s="30">
+        <v>1881997.8085183678</v>
+      </c>
+      <c r="K61" s="30">
+        <v>723504.77903614403</v>
+      </c>
+      <c r="L61" s="29">
+        <v>205613.75960413984</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20419,7 +20646,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23663,6 +23890,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="61" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-6554.9847565695836</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-5569.2306725832077</v>
+      </c>
+      <c r="G61" s="18">
+        <v>1727234.1261785296</v>
+      </c>
+      <c r="H61" s="18">
+        <v>2032954.6455786328</v>
+      </c>
+      <c r="I61" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J61" s="18">
+        <v>2130123.8005371881</v>
+      </c>
+      <c r="K61" s="18">
+        <v>810232.20843759482</v>
+      </c>
+      <c r="L61" s="17">
+        <v>97169.154958555227</v>
+      </c>
+      <c r="M61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="N61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="O61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="P61" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23679,7 +23956,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26923,6 +27200,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="61" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-54389.65209982227</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-46210.40780329454</v>
+      </c>
+      <c r="G61" s="18">
+        <v>14824747.516673513</v>
+      </c>
+      <c r="H61" s="18">
+        <v>17448728.50574781</v>
+      </c>
+      <c r="I61" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J61" s="18">
+        <v>18043573.156056687</v>
+      </c>
+      <c r="K61" s="18">
+        <v>7155737.3825757094</v>
+      </c>
+      <c r="L61" s="17">
+        <v>594844.65030887653</v>
+      </c>
+      <c r="M61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="N61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="O61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="P61" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -26939,7 +27266,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30543,6 +30870,62 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="61" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="17">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="17">
+        <v>-2847.4210998735844</v>
+      </c>
+      <c r="H61" s="18">
+        <v>-2419.2191921244844</v>
+      </c>
+      <c r="I61" s="18">
+        <v>1985748.7729419891</v>
+      </c>
+      <c r="J61" s="18">
+        <v>2337226.3966530859</v>
+      </c>
+      <c r="K61" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L61" s="18">
+        <v>2383797.0624165004</v>
+      </c>
+      <c r="M61" s="18">
+        <v>1064701.4707485952</v>
+      </c>
+      <c r="N61" s="17">
+        <v>46570.665763414443</v>
+      </c>
+      <c r="O61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="P61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="Q61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -30559,7 +30942,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -33996,6 +34379,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="61" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-27846.153362916037</v>
+      </c>
+      <c r="G61" s="18">
+        <v>1449800.8443679775</v>
+      </c>
+      <c r="H61" s="18">
+        <v>1706415.6601877252</v>
+      </c>
+      <c r="I61" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J61" s="18">
+        <v>1912029.4197918652</v>
+      </c>
+      <c r="K61" s="18">
+        <v>737217.62389631267</v>
+      </c>
+      <c r="L61" s="17">
+        <v>205613.75960413984</v>
+      </c>
+      <c r="M61" s="21">
+        <v>96.011413524955756</v>
+      </c>
+      <c r="N61" s="21">
+        <v>83.590090588113569</v>
+      </c>
+      <c r="O61" s="21">
+        <v>81.129632711666943</v>
+      </c>
+      <c r="P61" s="21">
+        <v>88.511006341006805</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -34012,7 +34448,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36936,6 +37372,50 @@
         <v>576916.65487642318</v>
       </c>
     </row>
+    <row r="61" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="17">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="17">
+        <v>-102248.30313182416</v>
+      </c>
+      <c r="H61" s="18">
+        <v>-86871.961899015572</v>
+      </c>
+      <c r="I61" s="18">
+        <v>12147924.632001366</v>
+      </c>
+      <c r="J61" s="18">
+        <v>14298107.847953467</v>
+      </c>
+      <c r="K61" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L61" s="18">
+        <v>14977272.805961713</v>
+      </c>
+      <c r="M61" s="18">
+        <v>6701632.8126654383</v>
+      </c>
+      <c r="N61" s="17">
+        <v>679164.95800824731</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -36952,7 +37432,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -39519,6 +39999,44 @@
         <v>955105.75082399882</v>
       </c>
     </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="18">
+        <v>12243926.091061944</v>
+      </c>
+      <c r="H61" s="18">
+        <v>14411101.569662364</v>
+      </c>
+      <c r="I61" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J61" s="18">
+        <v>15638155.580985475</v>
+      </c>
+      <c r="K61" s="18">
+        <v>6276820.7632580511</v>
+      </c>
+      <c r="L61" s="17">
+        <v>1227054.0113231102</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(RSI&KDJ).xlsx
@@ -587,7 +587,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -764,6 +764,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -773,7 +776,7 @@
               <c:f>'model2(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -949,6 +952,9 @@
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1158493.0294822238</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1158493.0294822238</c:v>
                 </c:pt>
               </c:numCache>
@@ -992,7 +998,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1169,6 +1175,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1178,7 +1187,7 @@
               <c:f>'model2(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1355,6 +1364,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1881997.8085183678</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1978849.1612350328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1397,7 +1409,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1574,6 +1586,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1583,7 +1598,7 @@
               <c:f>'model2(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1760,6 +1775,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>723504.77903614403</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>820356.13175280904</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1781,11 +1799,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="643962752"/>
-        <c:axId val="643964288"/>
+        <c:axId val="442374016"/>
+        <c:axId val="448737280"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="643962752"/>
+        <c:axId val="442374016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1828,14 +1846,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="643964288"/>
+        <c:crossAx val="448737280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="643964288"/>
+        <c:axId val="448737280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1886,7 +1904,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="643962752"/>
+        <c:crossAx val="442374016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2047,7 +2065,7 @@
               <c:f>'model2(1)&amp;KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2224,6 +2242,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2243,8 +2264,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="479033600"/>
-        <c:axId val="479032064"/>
+        <c:axId val="442312192"/>
+        <c:axId val="442310656"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2269,7 +2290,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2446,6 +2467,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2455,7 +2479,7 @@
               <c:f>'model2(1)&amp;KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2632,6 +2656,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2653,11 +2680,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479024640"/>
-        <c:axId val="479026176"/>
+        <c:axId val="442307328"/>
+        <c:axId val="442308864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479024640"/>
+        <c:axId val="442307328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2700,14 +2727,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479026176"/>
+        <c:crossAx val="442308864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479026176"/>
+        <c:axId val="442308864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2758,12 +2785,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479024640"/>
+        <c:crossAx val="442307328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="479032064"/>
+        <c:axId val="442310656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2800,12 +2827,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479033600"/>
+        <c:crossAx val="442312192"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="479033600"/>
+        <c:axId val="442312192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2814,7 +2841,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="479032064"/>
+        <c:crossAx val="442310656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2964,7 +2991,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3141,6 +3168,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3150,7 +3180,7 @@
               <c:f>'model2(2)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3326,6 +3356,9 @@
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>8275639.9932962749</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>8275639.9932962749</c:v>
                 </c:pt>
               </c:numCache>
@@ -3369,7 +3402,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3546,6 +3579,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3555,7 +3591,7 @@
               <c:f>'model2(2)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3732,6 +3768,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>14977272.805961713</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>15803331.182775768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3774,7 +3813,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3951,6 +3990,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3960,7 +4002,7 @@
               <c:f>'model2(2)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4137,6 +4179,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6701632.8126654383</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7527691.1894794926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4158,11 +4203,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479065600"/>
-        <c:axId val="479067136"/>
+        <c:axId val="442327808"/>
+        <c:axId val="442329344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479065600"/>
+        <c:axId val="442327808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4205,14 +4250,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479067136"/>
+        <c:crossAx val="442329344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479067136"/>
+        <c:axId val="442329344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4263,7 +4308,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479065600"/>
+        <c:crossAx val="442327808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4424,7 +4469,7 @@
               <c:f>'model2(2)vol'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4601,6 +4646,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-102248.30313182416</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-228232.84251096987</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4620,8 +4668,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="481208960"/>
-        <c:axId val="481207424"/>
+        <c:axId val="442353536"/>
+        <c:axId val="442352000"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4646,7 +4694,7 @@
               <c:f>'model2(2)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4823,6 +4871,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4832,7 +4883,7 @@
               <c:f>'model2(2)vol'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5009,6 +5060,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5030,11 +5084,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="481200000"/>
-        <c:axId val="481201536"/>
+        <c:axId val="442344576"/>
+        <c:axId val="442346112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="481200000"/>
+        <c:axId val="442344576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5077,14 +5131,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481201536"/>
+        <c:crossAx val="442346112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="481201536"/>
+        <c:axId val="442346112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5135,12 +5189,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481200000"/>
+        <c:crossAx val="442344576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="481207424"/>
+        <c:axId val="442352000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5177,12 +5231,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481208960"/>
+        <c:crossAx val="442353536"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="481208960"/>
+        <c:axId val="442353536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5191,7 +5245,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="481207424"/>
+        <c:crossAx val="442352000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5341,7 +5395,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5518,6 +5572,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5527,7 +5584,7 @@
               <c:f>'model2(2)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5703,6 +5760,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -5746,7 +5806,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5923,6 +5983,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5932,7 +5995,7 @@
               <c:f>'model2(2)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6109,6 +6172,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>15638155.580985475</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16470742.053078819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6151,7 +6217,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6328,6 +6394,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6337,7 +6406,7 @@
               <c:f>'model2(2)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6514,6 +6583,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6276820.7632580511</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7109407.2353513949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6535,11 +6607,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="481355648"/>
-        <c:axId val="481357184"/>
+        <c:axId val="452650112"/>
+        <c:axId val="452651648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="481355648"/>
+        <c:axId val="452650112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6582,14 +6654,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481357184"/>
+        <c:crossAx val="452651648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="481357184"/>
+        <c:axId val="452651648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6640,7 +6712,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481355648"/>
+        <c:crossAx val="452650112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6801,7 +6873,7 @@
               <c:f>'model2(2)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6978,6 +7050,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6997,8 +7072,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="481553408"/>
-        <c:axId val="481551872"/>
+        <c:axId val="453163264"/>
+        <c:axId val="453161728"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7023,7 +7098,7 @@
               <c:f>'model2(2)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7200,6 +7275,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7209,7 +7287,7 @@
               <c:f>'model2(2)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7386,6 +7464,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7407,11 +7488,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="481540352"/>
-        <c:axId val="481550336"/>
+        <c:axId val="453150208"/>
+        <c:axId val="453151744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="481540352"/>
+        <c:axId val="453150208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7454,14 +7535,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481550336"/>
+        <c:crossAx val="453151744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="481550336"/>
+        <c:axId val="453151744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7512,12 +7593,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481540352"/>
+        <c:crossAx val="453150208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="481551872"/>
+        <c:axId val="453161728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7554,12 +7635,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481553408"/>
+        <c:crossAx val="453163264"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="481553408"/>
+        <c:axId val="453163264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7568,7 +7649,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="481551872"/>
+        <c:crossAx val="453161728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7700,7 +7781,7 @@
               <c:f>'model2(1)'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7877,6 +7958,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7896,8 +7980,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="458522624"/>
-        <c:axId val="458520832"/>
+        <c:axId val="537083264"/>
+        <c:axId val="533669760"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7922,7 +8006,7 @@
               <c:f>'model2(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8099,6 +8183,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8108,7 +8195,7 @@
               <c:f>'model2(1)'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8285,6 +8372,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8306,11 +8396,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="458513408"/>
-        <c:axId val="458519296"/>
+        <c:axId val="524069120"/>
+        <c:axId val="533668224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="458513408"/>
+        <c:axId val="524069120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8353,14 +8443,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458519296"/>
+        <c:crossAx val="533668224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="458519296"/>
+        <c:axId val="533668224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8411,12 +8501,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458513408"/>
+        <c:crossAx val="524069120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="458520832"/>
+        <c:axId val="533669760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8453,12 +8543,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458522624"/>
+        <c:crossAx val="537083264"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="458522624"/>
+        <c:axId val="537083264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8467,7 +8557,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="458520832"/>
+        <c:crossAx val="533669760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8617,7 +8707,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8794,6 +8884,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8803,7 +8896,7 @@
               <c:f>'model2(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8979,6 +9072,9 @@
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1319891.5920995933</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1319891.5920995933</c:v>
                 </c:pt>
               </c:numCache>
@@ -9022,7 +9118,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9199,6 +9295,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9208,7 +9307,7 @@
               <c:f>'model2(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9385,6 +9484,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>2130123.8005371881</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2247575.650286919</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9427,7 +9529,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9604,6 +9706,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9613,7 +9718,7 @@
               <c:f>'model2(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9790,6 +9895,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>810232.20843759482</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>927684.05818732572</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9811,11 +9919,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="458537984"/>
-        <c:axId val="458547968"/>
+        <c:axId val="542306688"/>
+        <c:axId val="542308224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="458537984"/>
+        <c:axId val="542306688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9858,14 +9966,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458547968"/>
+        <c:crossAx val="542308224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="458547968"/>
+        <c:axId val="542308224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9916,7 +10024,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458537984"/>
+        <c:crossAx val="542306688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10098,7 +10206,7 @@
               <c:f>'model2(1)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10275,6 +10383,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-6554.9847565695836</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10294,8 +10405,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="459490048"/>
-        <c:axId val="459484160"/>
+        <c:axId val="399474688"/>
+        <c:axId val="399472896"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10320,7 +10431,7 @@
               <c:f>'model2(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10497,6 +10608,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10506,7 +10620,7 @@
               <c:f>'model2(1)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10683,6 +10797,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10704,11 +10821,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="459481088"/>
-        <c:axId val="459482624"/>
+        <c:axId val="614939648"/>
+        <c:axId val="399471360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="459481088"/>
+        <c:axId val="614939648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10751,14 +10868,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459482624"/>
+        <c:crossAx val="399471360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="459482624"/>
+        <c:axId val="399471360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10809,12 +10926,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459481088"/>
+        <c:crossAx val="614939648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="459484160"/>
+        <c:axId val="399472896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10851,12 +10968,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="459490048"/>
+        <c:crossAx val="399474688"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="459490048"/>
+        <c:axId val="399474688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10865,7 +10982,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="459484160"/>
+        <c:crossAx val="399472896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11015,7 +11132,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11192,6 +11309,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11201,7 +11321,7 @@
               <c:f>'model2(2)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11377,6 +11497,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -11420,7 +11543,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11597,6 +11720,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11606,7 +11732,7 @@
               <c:f>'model2(2)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11783,6 +11909,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>18043573.156056687</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19051655.379257303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11825,7 +11954,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12002,6 +12131,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12011,7 +12143,7 @@
               <c:f>'model2(2)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12188,6 +12320,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>7155737.3825757094</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>8163819.6057763249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12209,11 +12344,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="460894208"/>
-        <c:axId val="460895744"/>
+        <c:axId val="401497088"/>
+        <c:axId val="401507072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="460894208"/>
+        <c:axId val="401497088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12256,14 +12391,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460895744"/>
+        <c:crossAx val="401507072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="460895744"/>
+        <c:axId val="401507072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12314,7 +12449,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="460894208"/>
+        <c:crossAx val="401497088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12496,7 +12631,7 @@
               <c:f>'model2(2)&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12673,6 +12808,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-54389.65209982227</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12692,8 +12830,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="478746496"/>
-        <c:axId val="478744960"/>
+        <c:axId val="401523456"/>
+        <c:axId val="401521664"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12718,7 +12856,7 @@
               <c:f>'model2(2)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12895,6 +13033,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12904,7 +13045,7 @@
               <c:f>'model2(2)&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13081,6 +13222,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13102,11 +13246,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467010688"/>
-        <c:axId val="467012224"/>
+        <c:axId val="401518592"/>
+        <c:axId val="401520128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467010688"/>
+        <c:axId val="401518592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13149,14 +13293,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467012224"/>
+        <c:crossAx val="401520128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467012224"/>
+        <c:axId val="401520128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13207,12 +13351,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467010688"/>
+        <c:crossAx val="401518592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="478744960"/>
+        <c:axId val="401521664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13249,12 +13393,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478746496"/>
+        <c:crossAx val="401523456"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="478746496"/>
+        <c:axId val="401523456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13263,7 +13407,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="478744960"/>
+        <c:crossAx val="401521664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13413,7 +13557,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13590,6 +13734,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13599,7 +13746,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13775,6 +13922,9 @@
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1319095.5916679052</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1319095.5916679052</c:v>
                 </c:pt>
               </c:numCache>
@@ -13818,7 +13968,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13995,6 +14145,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14004,7 +14157,7 @@
               <c:f>'model2(2)vol&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14181,6 +14334,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>2383797.0624165004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2518827.8975449791</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14223,7 +14379,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14400,6 +14556,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14409,7 +14568,7 @@
               <c:f>'model2(2)vol&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14586,6 +14745,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1064701.4707485952</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1199732.3058770739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14607,11 +14769,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="478778112"/>
-        <c:axId val="478779648"/>
+        <c:axId val="426328064"/>
+        <c:axId val="426329600"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="478778112"/>
+        <c:axId val="426328064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14654,14 +14816,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478779648"/>
+        <c:crossAx val="426329600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="478779648"/>
+        <c:axId val="426329600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14712,7 +14874,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478778112"/>
+        <c:crossAx val="426328064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14873,7 +15035,7 @@
               <c:f>'model2(2)vol&amp;RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15050,6 +15212,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-2847.4210998735844</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-31779.256552160365</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15069,8 +15234,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="478926720"/>
-        <c:axId val="478925184"/>
+        <c:axId val="426349696"/>
+        <c:axId val="426347904"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15095,7 +15260,7 @@
               <c:f>'model2(2)vol&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15272,6 +15437,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15281,7 +15449,7 @@
               <c:f>'model2(2)vol&amp;RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15458,6 +15626,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15479,11 +15650,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="478889088"/>
-        <c:axId val="478890624"/>
+        <c:axId val="426344832"/>
+        <c:axId val="426346368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="478889088"/>
+        <c:axId val="426344832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15526,14 +15697,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478890624"/>
+        <c:crossAx val="426346368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="478890624"/>
+        <c:axId val="426346368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15584,12 +15755,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478889088"/>
+        <c:crossAx val="426344832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="478925184"/>
+        <c:axId val="426347904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15626,12 +15797,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478926720"/>
+        <c:crossAx val="426349696"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="478926720"/>
+        <c:axId val="426349696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15640,7 +15811,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="478925184"/>
+        <c:crossAx val="426347904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15790,7 +15961,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15967,6 +16138,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15976,7 +16150,7 @@
               <c:f>'model2(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16152,6 +16326,9 @@
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1174811.7958955525</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1174811.7958955525</c:v>
                 </c:pt>
               </c:numCache>
@@ -16195,7 +16372,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16372,6 +16549,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16381,7 +16561,7 @@
               <c:f>'model2(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16558,6 +16738,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1912029.4197918652</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2010615.8177554612</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16600,7 +16783,7 @@
               <c:f>'model2(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16777,6 +16960,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16786,7 +16972,7 @@
               <c:f>'model2(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16963,6 +17149,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>737217.62389631267</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>835804.02185990871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16984,11 +17173,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="478995584"/>
-        <c:axId val="478997120"/>
+        <c:axId val="440316288"/>
+        <c:axId val="440317824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="478995584"/>
+        <c:axId val="440316288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17031,14 +17220,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478997120"/>
+        <c:crossAx val="440317824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="478997120"/>
+        <c:axId val="440317824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17089,7 +17278,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="478995584"/>
+        <c:crossAx val="440316288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18025,7 +18214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -20630,6 +20819,44 @@
         <v>205613.75960413984</v>
       </c>
     </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="32">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="31">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="29">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="29">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F62" s="30">
+        <v>-28961.740190508626</v>
+      </c>
+      <c r="G62" s="30">
+        <v>1395323.7175117971</v>
+      </c>
+      <c r="H62" s="30">
+        <v>1737178.0349556094</v>
+      </c>
+      <c r="I62" s="30">
+        <v>1158493.0294822238</v>
+      </c>
+      <c r="J62" s="30">
+        <v>1978849.1612350328</v>
+      </c>
+      <c r="K62" s="30">
+        <v>820356.13175280904</v>
+      </c>
+      <c r="L62" s="29">
+        <v>241671.12627942342</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -20646,7 +20873,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23940,6 +24167,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="62" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-28961.740190508626</v>
+      </c>
+      <c r="G62" s="18">
+        <v>1698272.385988021</v>
+      </c>
+      <c r="H62" s="18">
+        <v>2114349.1286530802</v>
+      </c>
+      <c r="I62" s="18">
+        <v>1319891.5920995933</v>
+      </c>
+      <c r="J62" s="18">
+        <v>2247575.650286919</v>
+      </c>
+      <c r="K62" s="18">
+        <v>927684.05818732572</v>
+      </c>
+      <c r="L62" s="17">
+        <v>133226.5216338388</v>
+      </c>
+      <c r="M62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P62" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -23956,7 +24233,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27250,6 +27527,56 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="62" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="18">
+        <v>14560371.798799217</v>
+      </c>
+      <c r="H62" s="18">
+        <v>18127662.958934288</v>
+      </c>
+      <c r="I62" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J62" s="18">
+        <v>19051655.379257303</v>
+      </c>
+      <c r="K62" s="18">
+        <v>8163819.6057763249</v>
+      </c>
+      <c r="L62" s="17">
+        <v>923992.42032301589</v>
+      </c>
+      <c r="M62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P62" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -27266,7 +27593,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30926,6 +31253,62 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="62" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="17">
+        <v>-31779.256552160365</v>
+      </c>
+      <c r="H62" s="18">
+        <v>-25525.507173048401</v>
+      </c>
+      <c r="I62" s="18">
+        <v>1960223.2657689408</v>
+      </c>
+      <c r="J62" s="18">
+        <v>2440477.9752294044</v>
+      </c>
+      <c r="K62" s="18">
+        <v>1319095.5916679052</v>
+      </c>
+      <c r="L62" s="18">
+        <v>2518827.8975449791</v>
+      </c>
+      <c r="M62" s="18">
+        <v>1199732.3058770739</v>
+      </c>
+      <c r="N62" s="17">
+        <v>78349.922315574804</v>
+      </c>
+      <c r="O62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="P62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="Q62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="R62" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -30942,7 +31325,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34432,6 +34815,59 @@
         <v>1</v>
       </c>
     </row>
+    <row r="62" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-28961.740190508626</v>
+      </c>
+      <c r="G62" s="18">
+        <v>1420839.1041774689</v>
+      </c>
+      <c r="H62" s="18">
+        <v>1768944.6914760377</v>
+      </c>
+      <c r="I62" s="18">
+        <v>1174811.7958955525</v>
+      </c>
+      <c r="J62" s="18">
+        <v>2010615.8177554612</v>
+      </c>
+      <c r="K62" s="18">
+        <v>835804.02185990871</v>
+      </c>
+      <c r="L62" s="17">
+        <v>241671.12627942342</v>
+      </c>
+      <c r="M62" s="21">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="N62" s="21">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="O62" s="21">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="P62" s="21">
+        <v>94.913940221952458</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
@@ -34448,7 +34884,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37416,6 +37852,50 @@
         <v>679164.95800824731</v>
       </c>
     </row>
+    <row r="62" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="17">
+        <v>-228232.84251096987</v>
+      </c>
+      <c r="H62" s="18">
+        <v>-183319.55151552943</v>
+      </c>
+      <c r="I62" s="18">
+        <v>11964605.080485838</v>
+      </c>
+      <c r="J62" s="18">
+        <v>14895933.382256551</v>
+      </c>
+      <c r="K62" s="18">
+        <v>8275639.9932962749</v>
+      </c>
+      <c r="L62" s="18">
+        <v>15803331.182775768</v>
+      </c>
+      <c r="M62" s="18">
+        <v>7527691.1894794926</v>
+      </c>
+      <c r="N62" s="17">
+        <v>907397.80051921715</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="J2">
@@ -37432,7 +37912,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -40037,6 +40517,44 @@
         <v>1227054.0113231102</v>
       </c>
     </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="18">
+        <v>11979550.373187648</v>
+      </c>
+      <c r="H62" s="18">
+        <v>14914540.271741569</v>
+      </c>
+      <c r="I62" s="18">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J62" s="18">
+        <v>16470742.053078819</v>
+      </c>
+      <c r="K62" s="18">
+        <v>7109407.2353513949</v>
+      </c>
+      <c r="L62" s="17">
+        <v>1556201.7813372496</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
